--- a/3_Validation_and_Development/NOVA_Development_Archive.xlsx
+++ b/3_Validation_and_Development/NOVA_Development_Archive.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archive" sheetId="1" r:id="R2543fea221b543b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refinements" sheetId="2" r:id="R176afed572c049b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archive" sheetId="1" r:id="Rf2345c5463054a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refinements" sheetId="2" r:id="R2b6b875b4f134a85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -350,7 +350,7 @@
         <x:v>d1</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>Researcher example</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -366,7 +366,7 @@
         <x:v>d2</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>Researcher example with generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -385,7 +385,7 @@
         <x:v>d3</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>Researcher example</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -402,7 +402,7 @@
         <x:v>d4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>Researcher example</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -419,7 +419,7 @@
         <x:v>d5</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -434,7 +434,7 @@
         <x:v>d6</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -449,7 +449,7 @@
         <x:v>d7</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -464,7 +464,7 @@
         <x:v>d8</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -479,7 +479,7 @@
         <x:v>d9</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -494,7 +494,7 @@
         <x:v>d10</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -509,7 +509,7 @@
         <x:v>d11</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -524,7 +524,7 @@
         <x:v>d12</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -539,7 +539,7 @@
         <x:v>d13</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -554,7 +554,7 @@
         <x:v>d14</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -569,7 +569,7 @@
         <x:v>d15</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -584,7 +584,7 @@
         <x:v>d16</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -599,7 +599,7 @@
         <x:v>d17</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -614,7 +614,7 @@
         <x:v>d18</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -629,7 +629,7 @@
         <x:v>d19</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -644,7 +644,7 @@
         <x:v>d20</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -659,7 +659,7 @@
         <x:v>d21</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -674,7 +674,7 @@
         <x:v>d22</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -689,7 +689,7 @@
         <x:v>d23</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -704,7 +704,7 @@
         <x:v>d24</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -719,7 +719,7 @@
         <x:v>d25</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -734,7 +734,7 @@
         <x:v>d26</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -749,7 +749,7 @@
         <x:v>d27</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -764,7 +764,7 @@
         <x:v>d28</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -779,7 +779,7 @@
         <x:v>d29</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -794,7 +794,7 @@
         <x:v>d30</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -809,7 +809,7 @@
         <x:v>d31</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C32" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -824,7 +824,7 @@
         <x:v>d32</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -839,7 +839,7 @@
         <x:v>d33</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -854,7 +854,7 @@
         <x:v>d34</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -869,7 +869,7 @@
         <x:v>d35</x:v>
       </x:c>
       <x:c r="B36" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -884,7 +884,7 @@
         <x:v>d36</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -899,7 +899,7 @@
         <x:v>d37</x:v>
       </x:c>
       <x:c r="B38" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C38" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -914,7 +914,7 @@
         <x:v>d38</x:v>
       </x:c>
       <x:c r="B39" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C39" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -929,7 +929,7 @@
         <x:v>d39</x:v>
       </x:c>
       <x:c r="B40" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C40" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -944,7 +944,7 @@
         <x:v>d40</x:v>
       </x:c>
       <x:c r="B41" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C41" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -959,7 +959,7 @@
         <x:v>d41</x:v>
       </x:c>
       <x:c r="B42" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C42" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -974,7 +974,7 @@
         <x:v>d42</x:v>
       </x:c>
       <x:c r="B43" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C43" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -989,7 +989,7 @@
         <x:v>d43</x:v>
       </x:c>
       <x:c r="B44" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C44" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1004,7 +1004,7 @@
         <x:v>d44</x:v>
       </x:c>
       <x:c r="B45" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C45" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1019,7 +1019,7 @@
         <x:v>d45</x:v>
       </x:c>
       <x:c r="B46" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C46" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1034,7 +1034,7 @@
         <x:v>d46</x:v>
       </x:c>
       <x:c r="B47" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Wording from an earlier LLM negotiation</x:v>
+        <x:v>LLM to LLM negotiation</x:v>
       </x:c>
       <x:c r="C47" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>d47</x:v>
       </x:c>
       <x:c r="B48" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C48" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1064,7 +1064,7 @@
         <x:v>d48</x:v>
       </x:c>
       <x:c r="B49" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C49" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1080,7 +1080,7 @@
         <x:v>d49</x:v>
       </x:c>
       <x:c r="B50" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C50" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1095,7 +1095,7 @@
         <x:v>d50</x:v>
       </x:c>
       <x:c r="B51" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C51" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1110,7 +1110,7 @@
         <x:v>d51</x:v>
       </x:c>
       <x:c r="B52" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C52" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>d52</x:v>
       </x:c>
       <x:c r="B53" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C53" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1140,7 +1140,7 @@
         <x:v>d53</x:v>
       </x:c>
       <x:c r="B54" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C54" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>d54</x:v>
       </x:c>
       <x:c r="B55" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C55" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1170,7 +1170,7 @@
         <x:v>d55</x:v>
       </x:c>
       <x:c r="B56" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C56" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1186,7 +1186,7 @@
         <x:v>d56</x:v>
       </x:c>
       <x:c r="B57" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C57" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1202,7 +1202,7 @@
         <x:v>d57</x:v>
       </x:c>
       <x:c r="B58" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C58" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1217,7 +1217,7 @@
         <x:v>d58</x:v>
       </x:c>
       <x:c r="B59" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C59" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1232,7 +1232,7 @@
         <x:v>d59</x:v>
       </x:c>
       <x:c r="B60" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C60" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1247,7 +1247,7 @@
         <x:v>d60</x:v>
       </x:c>
       <x:c r="B61" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C61" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>d61</x:v>
       </x:c>
       <x:c r="B62" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C62" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1277,7 +1277,7 @@
         <x:v>d62</x:v>
       </x:c>
       <x:c r="B63" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C63" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1292,7 +1292,7 @@
         <x:v>d63</x:v>
       </x:c>
       <x:c r="B64" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C64" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1302,12 +1302,12 @@
       </x:c>
       <x:c r="E64" s="5" t="str"/>
     </x:row>
-    <x:row r="65" ht="51" customHeight="1">
+    <x:row r="65" ht="61.5" customHeight="1">
       <x:c r="A65" s="6" t="str">
         <x:v>d64</x:v>
       </x:c>
       <x:c r="B65" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C65" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1317,12 +1317,12 @@
       </x:c>
       <x:c r="E65" s="5" t="str"/>
     </x:row>
-    <x:row r="66" ht="51" customHeight="1">
+    <x:row r="66" ht="61.5" customHeight="1">
       <x:c r="A66" s="6" t="str">
         <x:v>d65</x:v>
       </x:c>
       <x:c r="B66" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C66" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1332,12 +1332,12 @@
       </x:c>
       <x:c r="E66" s="5" t="str"/>
     </x:row>
-    <x:row r="67" ht="51" customHeight="1">
+    <x:row r="67" ht="61.5" customHeight="1">
       <x:c r="A67" s="6" t="str">
         <x:v>d66</x:v>
       </x:c>
       <x:c r="B67" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C67" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1347,12 +1347,12 @@
       </x:c>
       <x:c r="E67" s="5" t="str"/>
     </x:row>
-    <x:row r="68" ht="51" customHeight="1">
+    <x:row r="68" ht="61.5" customHeight="1">
       <x:c r="A68" s="6" t="str">
         <x:v>d67</x:v>
       </x:c>
       <x:c r="B68" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C68" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1362,12 +1362,12 @@
       </x:c>
       <x:c r="E68" s="5" t="str"/>
     </x:row>
-    <x:row r="69" ht="51" customHeight="1">
+    <x:row r="69" ht="61.5" customHeight="1">
       <x:c r="A69" s="6" t="str">
         <x:v>d68</x:v>
       </x:c>
       <x:c r="B69" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C69" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1378,12 +1378,12 @@
       </x:c>
       <x:c r="E69" s="5" t="str"/>
     </x:row>
-    <x:row r="70" ht="51" customHeight="1">
+    <x:row r="70" ht="61.5" customHeight="1">
       <x:c r="A70" s="6" t="str">
         <x:v>d69</x:v>
       </x:c>
       <x:c r="B70" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C70" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1393,12 +1393,12 @@
       </x:c>
       <x:c r="E70" s="5" t="str"/>
     </x:row>
-    <x:row r="71" ht="51" customHeight="1">
+    <x:row r="71" ht="61.5" customHeight="1">
       <x:c r="A71" s="6" t="str">
         <x:v>d70</x:v>
       </x:c>
       <x:c r="B71" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C71" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1408,12 +1408,12 @@
       </x:c>
       <x:c r="E71" s="5" t="str"/>
     </x:row>
-    <x:row r="72" ht="51" customHeight="1">
+    <x:row r="72" ht="61.5" customHeight="1">
       <x:c r="A72" s="6" t="str">
         <x:v>d71</x:v>
       </x:c>
       <x:c r="B72" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C72" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1423,12 +1423,12 @@
       </x:c>
       <x:c r="E72" s="5" t="str"/>
     </x:row>
-    <x:row r="73" ht="51" customHeight="1">
+    <x:row r="73" ht="61.5" customHeight="1">
       <x:c r="A73" s="6" t="str">
         <x:v>d72</x:v>
       </x:c>
       <x:c r="B73" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C73" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1438,12 +1438,12 @@
       </x:c>
       <x:c r="E73" s="5" t="str"/>
     </x:row>
-    <x:row r="74" ht="51" customHeight="1">
+    <x:row r="74" ht="61.5" customHeight="1">
       <x:c r="A74" s="6" t="str">
         <x:v>d73</x:v>
       </x:c>
       <x:c r="B74" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C74" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1454,12 +1454,12 @@
       </x:c>
       <x:c r="E74" s="5" t="str"/>
     </x:row>
-    <x:row r="75" ht="51" customHeight="1">
+    <x:row r="75" ht="61.5" customHeight="1">
       <x:c r="A75" s="6" t="str">
         <x:v>d74</x:v>
       </x:c>
       <x:c r="B75" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C75" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1469,12 +1469,12 @@
       </x:c>
       <x:c r="E75" s="5" t="str"/>
     </x:row>
-    <x:row r="76" ht="51" customHeight="1">
+    <x:row r="76" ht="61.5" customHeight="1">
       <x:c r="A76" s="6" t="str">
         <x:v>d75</x:v>
       </x:c>
       <x:c r="B76" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C76" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1484,12 +1484,12 @@
       </x:c>
       <x:c r="E76" s="5" t="str"/>
     </x:row>
-    <x:row r="77" ht="51" customHeight="1">
+    <x:row r="77" ht="61.5" customHeight="1">
       <x:c r="A77" s="6" t="str">
         <x:v>d76</x:v>
       </x:c>
       <x:c r="B77" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C77" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1499,12 +1499,12 @@
       </x:c>
       <x:c r="E77" s="5" t="str"/>
     </x:row>
-    <x:row r="78" ht="51" customHeight="1">
+    <x:row r="78" ht="61.5" customHeight="1">
       <x:c r="A78" s="6" t="str">
         <x:v>d77</x:v>
       </x:c>
       <x:c r="B78" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C78" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1514,12 +1514,12 @@
       </x:c>
       <x:c r="E78" s="5" t="str"/>
     </x:row>
-    <x:row r="79" ht="51" customHeight="1">
+    <x:row r="79" ht="61.5" customHeight="1">
       <x:c r="A79" s="6" t="str">
         <x:v>d78</x:v>
       </x:c>
       <x:c r="B79" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C79" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1530,12 +1530,12 @@
       </x:c>
       <x:c r="E79" s="5" t="str"/>
     </x:row>
-    <x:row r="80" ht="51" customHeight="1">
+    <x:row r="80" ht="61.5" customHeight="1">
       <x:c r="A80" s="6" t="str">
         <x:v>d79</x:v>
       </x:c>
       <x:c r="B80" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C80" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1545,12 +1545,12 @@
       </x:c>
       <x:c r="E80" s="5" t="str"/>
     </x:row>
-    <x:row r="81" ht="51" customHeight="1">
+    <x:row r="81" ht="61.5" customHeight="1">
       <x:c r="A81" s="6" t="str">
         <x:v>d80</x:v>
       </x:c>
       <x:c r="B81" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C81" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1560,12 +1560,12 @@
       </x:c>
       <x:c r="E81" s="5" t="str"/>
     </x:row>
-    <x:row r="82" ht="51" customHeight="1">
+    <x:row r="82" ht="61.5" customHeight="1">
       <x:c r="A82" s="6" t="str">
         <x:v>d81</x:v>
       </x:c>
       <x:c r="B82" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C82" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1575,12 +1575,12 @@
       </x:c>
       <x:c r="E82" s="5" t="str"/>
     </x:row>
-    <x:row r="83" ht="51" customHeight="1">
+    <x:row r="83" ht="61.5" customHeight="1">
       <x:c r="A83" s="6" t="str">
         <x:v>d82</x:v>
       </x:c>
       <x:c r="B83" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C83" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1590,12 +1590,12 @@
       </x:c>
       <x:c r="E83" s="5" t="str"/>
     </x:row>
-    <x:row r="84" ht="51" customHeight="1">
+    <x:row r="84" ht="61.5" customHeight="1">
       <x:c r="A84" s="6" t="str">
         <x:v>d83</x:v>
       </x:c>
       <x:c r="B84" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C84" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1606,12 +1606,12 @@
       </x:c>
       <x:c r="E84" s="5" t="str"/>
     </x:row>
-    <x:row r="85" ht="51" customHeight="1">
+    <x:row r="85" ht="61.5" customHeight="1">
       <x:c r="A85" s="6" t="str">
         <x:v>d84</x:v>
       </x:c>
       <x:c r="B85" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C85" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1621,12 +1621,12 @@
       </x:c>
       <x:c r="E85" s="5" t="str"/>
     </x:row>
-    <x:row r="86" ht="51" customHeight="1">
+    <x:row r="86" ht="61.5" customHeight="1">
       <x:c r="A86" s="6" t="str">
         <x:v>d85</x:v>
       </x:c>
       <x:c r="B86" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C86" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1636,12 +1636,12 @@
       </x:c>
       <x:c r="E86" s="5" t="str"/>
     </x:row>
-    <x:row r="87" ht="51" customHeight="1">
+    <x:row r="87" ht="61.5" customHeight="1">
       <x:c r="A87" s="6" t="str">
         <x:v>d86</x:v>
       </x:c>
       <x:c r="B87" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C87" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1651,12 +1651,12 @@
       </x:c>
       <x:c r="E87" s="5" t="str"/>
     </x:row>
-    <x:row r="88" ht="51" customHeight="1">
+    <x:row r="88" ht="61.5" customHeight="1">
       <x:c r="A88" s="6" t="str">
         <x:v>d87</x:v>
       </x:c>
       <x:c r="B88" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C88" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1666,12 +1666,12 @@
       </x:c>
       <x:c r="E88" s="5" t="str"/>
     </x:row>
-    <x:row r="89" ht="51" customHeight="1">
+    <x:row r="89" ht="61.5" customHeight="1">
       <x:c r="A89" s="6" t="str">
         <x:v>d88</x:v>
       </x:c>
       <x:c r="B89" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C89" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1682,12 +1682,12 @@
       </x:c>
       <x:c r="E89" s="5" t="str"/>
     </x:row>
-    <x:row r="90" ht="51" customHeight="1">
+    <x:row r="90" ht="61.5" customHeight="1">
       <x:c r="A90" s="6" t="str">
         <x:v>d89</x:v>
       </x:c>
       <x:c r="B90" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C90" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1697,12 +1697,12 @@
       </x:c>
       <x:c r="E90" s="5" t="str"/>
     </x:row>
-    <x:row r="91" ht="51" customHeight="1">
+    <x:row r="91" ht="61.5" customHeight="1">
       <x:c r="A91" s="6" t="str">
         <x:v>d90</x:v>
       </x:c>
       <x:c r="B91" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C91" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1712,12 +1712,12 @@
       </x:c>
       <x:c r="E91" s="5" t="str"/>
     </x:row>
-    <x:row r="92" ht="51" customHeight="1">
+    <x:row r="92" ht="61.5" customHeight="1">
       <x:c r="A92" s="6" t="str">
         <x:v>d91</x:v>
       </x:c>
       <x:c r="B92" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C92" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1727,12 +1727,12 @@
       </x:c>
       <x:c r="E92" s="5" t="str"/>
     </x:row>
-    <x:row r="93" ht="51" customHeight="1">
+    <x:row r="93" ht="61.5" customHeight="1">
       <x:c r="A93" s="6" t="str">
         <x:v>d92</x:v>
       </x:c>
       <x:c r="B93" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C93" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1742,12 +1742,12 @@
       </x:c>
       <x:c r="E93" s="5" t="str"/>
     </x:row>
-    <x:row r="94" ht="51" customHeight="1">
+    <x:row r="94" ht="61.5" customHeight="1">
       <x:c r="A94" s="6" t="str">
         <x:v>d93</x:v>
       </x:c>
       <x:c r="B94" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C94" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1758,12 +1758,12 @@
       </x:c>
       <x:c r="E94" s="5" t="str"/>
     </x:row>
-    <x:row r="95" ht="51" customHeight="1">
+    <x:row r="95" ht="61.5" customHeight="1">
       <x:c r="A95" s="6" t="str">
         <x:v>d94</x:v>
       </x:c>
       <x:c r="B95" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C95" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1773,12 +1773,12 @@
       </x:c>
       <x:c r="E95" s="5" t="str"/>
     </x:row>
-    <x:row r="96" ht="51" customHeight="1">
+    <x:row r="96" ht="61.5" customHeight="1">
       <x:c r="A96" s="6" t="str">
         <x:v>d95</x:v>
       </x:c>
       <x:c r="B96" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C96" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1788,12 +1788,12 @@
       </x:c>
       <x:c r="E96" s="5" t="str"/>
     </x:row>
-    <x:row r="97" ht="51" customHeight="1">
+    <x:row r="97" ht="61.5" customHeight="1">
       <x:c r="A97" s="6" t="str">
         <x:v>d96</x:v>
       </x:c>
       <x:c r="B97" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C97" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1803,12 +1803,12 @@
       </x:c>
       <x:c r="E97" s="5" t="str"/>
     </x:row>
-    <x:row r="98" ht="51" customHeight="1">
+    <x:row r="98" ht="61.5" customHeight="1">
       <x:c r="A98" s="6" t="str">
         <x:v>d97</x:v>
       </x:c>
       <x:c r="B98" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C98" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1818,12 +1818,12 @@
       </x:c>
       <x:c r="E98" s="5" t="str"/>
     </x:row>
-    <x:row r="99" ht="57.75" customHeight="1">
+    <x:row r="99" ht="61.5" customHeight="1">
       <x:c r="A99" s="6" t="str">
         <x:v>d98</x:v>
       </x:c>
       <x:c r="B99" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C99" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1834,12 +1834,12 @@
       </x:c>
       <x:c r="E99" s="5" t="str"/>
     </x:row>
-    <x:row r="100" ht="51" customHeight="1">
+    <x:row r="100" ht="61.5" customHeight="1">
       <x:c r="A100" s="6" t="str">
         <x:v>d99</x:v>
       </x:c>
       <x:c r="B100" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C100" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1849,12 +1849,12 @@
       </x:c>
       <x:c r="E100" s="5" t="str"/>
     </x:row>
-    <x:row r="101" ht="51" customHeight="1">
+    <x:row r="101" ht="61.5" customHeight="1">
       <x:c r="A101" s="6" t="str">
         <x:v>d100</x:v>
       </x:c>
       <x:c r="B101" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C101" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1864,12 +1864,12 @@
       </x:c>
       <x:c r="E101" s="5" t="str"/>
     </x:row>
-    <x:row r="102" ht="51" customHeight="1">
+    <x:row r="102" ht="61.5" customHeight="1">
       <x:c r="A102" s="6" t="str">
         <x:v>d101</x:v>
       </x:c>
       <x:c r="B102" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C102" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1879,12 +1879,12 @@
       </x:c>
       <x:c r="E102" s="5" t="str"/>
     </x:row>
-    <x:row r="103" ht="51" customHeight="1">
+    <x:row r="103" ht="61.5" customHeight="1">
       <x:c r="A103" s="6" t="str">
         <x:v>d102</x:v>
       </x:c>
       <x:c r="B103" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C103" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1894,12 +1894,12 @@
       </x:c>
       <x:c r="E103" s="5" t="str"/>
     </x:row>
-    <x:row r="104" ht="51" customHeight="1">
+    <x:row r="104" ht="61.5" customHeight="1">
       <x:c r="A104" s="6" t="str">
         <x:v>d103</x:v>
       </x:c>
       <x:c r="B104" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C104" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1910,12 +1910,12 @@
       </x:c>
       <x:c r="E104" s="5" t="str"/>
     </x:row>
-    <x:row r="105" ht="51" customHeight="1">
+    <x:row r="105" ht="61.5" customHeight="1">
       <x:c r="A105" s="6" t="str">
         <x:v>d104</x:v>
       </x:c>
       <x:c r="B105" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C105" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1925,12 +1925,12 @@
       </x:c>
       <x:c r="E105" s="5" t="str"/>
     </x:row>
-    <x:row r="106" ht="51" customHeight="1">
+    <x:row r="106" ht="61.5" customHeight="1">
       <x:c r="A106" s="6" t="str">
         <x:v>d105</x:v>
       </x:c>
       <x:c r="B106" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C106" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1940,12 +1940,12 @@
       </x:c>
       <x:c r="E106" s="5" t="str"/>
     </x:row>
-    <x:row r="107" ht="51" customHeight="1">
+    <x:row r="107" ht="61.5" customHeight="1">
       <x:c r="A107" s="6" t="str">
         <x:v>d106</x:v>
       </x:c>
       <x:c r="B107" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C107" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1955,12 +1955,12 @@
       </x:c>
       <x:c r="E107" s="5" t="str"/>
     </x:row>
-    <x:row r="108" ht="51" customHeight="1">
+    <x:row r="108" ht="61.5" customHeight="1">
       <x:c r="A108" s="6" t="str">
         <x:v>d107</x:v>
       </x:c>
       <x:c r="B108" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C108" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -1970,12 +1970,12 @@
       </x:c>
       <x:c r="E108" s="5" t="str"/>
     </x:row>
-    <x:row r="109" ht="51" customHeight="1">
+    <x:row r="109" ht="61.5" customHeight="1">
       <x:c r="A109" s="6" t="str">
         <x:v>d108</x:v>
       </x:c>
       <x:c r="B109" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C109" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -1986,12 +1986,12 @@
       </x:c>
       <x:c r="E109" s="5" t="str"/>
     </x:row>
-    <x:row r="110" ht="51" customHeight="1">
+    <x:row r="110" ht="61.5" customHeight="1">
       <x:c r="A110" s="6" t="str">
         <x:v>d109</x:v>
       </x:c>
       <x:c r="B110" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C110" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2001,12 +2001,12 @@
       </x:c>
       <x:c r="E110" s="5" t="str"/>
     </x:row>
-    <x:row r="111" ht="51" customHeight="1">
+    <x:row r="111" ht="61.5" customHeight="1">
       <x:c r="A111" s="6" t="str">
         <x:v>d110</x:v>
       </x:c>
       <x:c r="B111" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C111" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2016,12 +2016,12 @@
       </x:c>
       <x:c r="E111" s="5" t="str"/>
     </x:row>
-    <x:row r="112" ht="51" customHeight="1">
+    <x:row r="112" ht="61.5" customHeight="1">
       <x:c r="A112" s="6" t="str">
         <x:v>d111</x:v>
       </x:c>
       <x:c r="B112" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C112" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2031,12 +2031,12 @@
       </x:c>
       <x:c r="E112" s="5" t="str"/>
     </x:row>
-    <x:row r="113" ht="51" customHeight="1">
+    <x:row r="113" ht="61.5" customHeight="1">
       <x:c r="A113" s="6" t="str">
         <x:v>d112</x:v>
       </x:c>
       <x:c r="B113" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C113" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2046,12 +2046,12 @@
       </x:c>
       <x:c r="E113" s="5" t="str"/>
     </x:row>
-    <x:row r="114" ht="51" customHeight="1">
+    <x:row r="114" ht="61.5" customHeight="1">
       <x:c r="A114" s="6" t="str">
         <x:v>d113</x:v>
       </x:c>
       <x:c r="B114" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C114" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2062,12 +2062,12 @@
       </x:c>
       <x:c r="E114" s="5" t="str"/>
     </x:row>
-    <x:row r="115" ht="51" customHeight="1">
+    <x:row r="115" ht="61.5" customHeight="1">
       <x:c r="A115" s="6" t="str">
         <x:v>d114</x:v>
       </x:c>
       <x:c r="B115" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C115" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2077,12 +2077,12 @@
       </x:c>
       <x:c r="E115" s="5" t="str"/>
     </x:row>
-    <x:row r="116" ht="51" customHeight="1">
+    <x:row r="116" ht="61.5" customHeight="1">
       <x:c r="A116" s="6" t="str">
         <x:v>d115</x:v>
       </x:c>
       <x:c r="B116" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C116" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2092,12 +2092,12 @@
       </x:c>
       <x:c r="E116" s="5" t="str"/>
     </x:row>
-    <x:row r="117" ht="51" customHeight="1">
+    <x:row r="117" ht="61.5" customHeight="1">
       <x:c r="A117" s="6" t="str">
         <x:v>d116</x:v>
       </x:c>
       <x:c r="B117" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C117" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2107,12 +2107,12 @@
       </x:c>
       <x:c r="E117" s="5" t="str"/>
     </x:row>
-    <x:row r="118" ht="51" customHeight="1">
+    <x:row r="118" ht="61.5" customHeight="1">
       <x:c r="A118" s="6" t="str">
         <x:v>d117</x:v>
       </x:c>
       <x:c r="B118" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C118" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2122,12 +2122,12 @@
       </x:c>
       <x:c r="E118" s="5" t="str"/>
     </x:row>
-    <x:row r="119" ht="51" customHeight="1">
+    <x:row r="119" ht="61.5" customHeight="1">
       <x:c r="A119" s="6" t="str">
         <x:v>d118</x:v>
       </x:c>
       <x:c r="B119" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C119" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2138,12 +2138,12 @@
       </x:c>
       <x:c r="E119" s="5" t="str"/>
     </x:row>
-    <x:row r="120" ht="51" customHeight="1">
+    <x:row r="120" ht="61.5" customHeight="1">
       <x:c r="A120" s="6" t="str">
         <x:v>d119</x:v>
       </x:c>
       <x:c r="B120" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C120" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2153,12 +2153,12 @@
       </x:c>
       <x:c r="E120" s="5" t="str"/>
     </x:row>
-    <x:row r="121" ht="51" customHeight="1">
+    <x:row r="121" ht="61.5" customHeight="1">
       <x:c r="A121" s="6" t="str">
         <x:v>d120</x:v>
       </x:c>
       <x:c r="B121" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C121" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2168,12 +2168,12 @@
       </x:c>
       <x:c r="E121" s="5" t="str"/>
     </x:row>
-    <x:row r="122" ht="51" customHeight="1">
+    <x:row r="122" ht="61.5" customHeight="1">
       <x:c r="A122" s="6" t="str">
         <x:v>d121</x:v>
       </x:c>
       <x:c r="B122" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C122" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2183,12 +2183,12 @@
       </x:c>
       <x:c r="E122" s="5" t="str"/>
     </x:row>
-    <x:row r="123" ht="51" customHeight="1">
+    <x:row r="123" ht="61.5" customHeight="1">
       <x:c r="A123" s="6" t="str">
         <x:v>d122</x:v>
       </x:c>
       <x:c r="B123" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C123" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2198,12 +2198,12 @@
       </x:c>
       <x:c r="E123" s="5" t="str"/>
     </x:row>
-    <x:row r="124" ht="51" customHeight="1">
+    <x:row r="124" ht="61.5" customHeight="1">
       <x:c r="A124" s="6" t="str">
         <x:v>d123</x:v>
       </x:c>
       <x:c r="B124" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C124" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2214,12 +2214,12 @@
       </x:c>
       <x:c r="E124" s="5" t="str"/>
     </x:row>
-    <x:row r="125" ht="51" customHeight="1">
+    <x:row r="125" ht="61.5" customHeight="1">
       <x:c r="A125" s="6" t="str">
         <x:v>d124</x:v>
       </x:c>
       <x:c r="B125" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C125" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2229,12 +2229,12 @@
       </x:c>
       <x:c r="E125" s="5" t="str"/>
     </x:row>
-    <x:row r="126" ht="51" customHeight="1">
+    <x:row r="126" ht="61.5" customHeight="1">
       <x:c r="A126" s="6" t="str">
         <x:v>d125</x:v>
       </x:c>
       <x:c r="B126" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C126" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2244,12 +2244,12 @@
       </x:c>
       <x:c r="E126" s="5" t="str"/>
     </x:row>
-    <x:row r="127" ht="51" customHeight="1">
+    <x:row r="127" ht="61.5" customHeight="1">
       <x:c r="A127" s="6" t="str">
         <x:v>d126</x:v>
       </x:c>
       <x:c r="B127" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C127" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2259,12 +2259,12 @@
       </x:c>
       <x:c r="E127" s="5" t="str"/>
     </x:row>
-    <x:row r="128" ht="51" customHeight="1">
+    <x:row r="128" ht="61.5" customHeight="1">
       <x:c r="A128" s="6" t="str">
         <x:v>d127</x:v>
       </x:c>
       <x:c r="B128" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C128" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2274,12 +2274,12 @@
       </x:c>
       <x:c r="E128" s="5" t="str"/>
     </x:row>
-    <x:row r="129" ht="51" customHeight="1">
+    <x:row r="129" ht="61.5" customHeight="1">
       <x:c r="A129" s="6" t="str">
         <x:v>d128</x:v>
       </x:c>
       <x:c r="B129" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C129" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2290,12 +2290,12 @@
       </x:c>
       <x:c r="E129" s="5" t="str"/>
     </x:row>
-    <x:row r="130" ht="51" customHeight="1">
+    <x:row r="130" ht="61.5" customHeight="1">
       <x:c r="A130" s="6" t="str">
         <x:v>d129</x:v>
       </x:c>
       <x:c r="B130" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C130" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2305,12 +2305,12 @@
       </x:c>
       <x:c r="E130" s="5" t="str"/>
     </x:row>
-    <x:row r="131" ht="51" customHeight="1">
+    <x:row r="131" ht="61.5" customHeight="1">
       <x:c r="A131" s="6" t="str">
         <x:v>d130</x:v>
       </x:c>
       <x:c r="B131" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C131" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2320,12 +2320,12 @@
       </x:c>
       <x:c r="E131" s="5" t="str"/>
     </x:row>
-    <x:row r="132" ht="51" customHeight="1">
+    <x:row r="132" ht="61.5" customHeight="1">
       <x:c r="A132" s="6" t="str">
         <x:v>d131</x:v>
       </x:c>
       <x:c r="B132" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C132" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2335,12 +2335,12 @@
       </x:c>
       <x:c r="E132" s="5" t="str"/>
     </x:row>
-    <x:row r="133" ht="51" customHeight="1">
+    <x:row r="133" ht="61.5" customHeight="1">
       <x:c r="A133" s="6" t="str">
         <x:v>d132</x:v>
       </x:c>
       <x:c r="B133" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C133" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2350,12 +2350,12 @@
       </x:c>
       <x:c r="E133" s="5" t="str"/>
     </x:row>
-    <x:row r="134" ht="51" customHeight="1">
+    <x:row r="134" ht="61.5" customHeight="1">
       <x:c r="A134" s="6" t="str">
         <x:v>d133</x:v>
       </x:c>
       <x:c r="B134" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C134" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2366,12 +2366,12 @@
       </x:c>
       <x:c r="E134" s="5" t="str"/>
     </x:row>
-    <x:row r="135" ht="51" customHeight="1">
+    <x:row r="135" ht="61.5" customHeight="1">
       <x:c r="A135" s="6" t="str">
         <x:v>d134</x:v>
       </x:c>
       <x:c r="B135" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C135" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2381,12 +2381,12 @@
       </x:c>
       <x:c r="E135" s="5" t="str"/>
     </x:row>
-    <x:row r="136" ht="51" customHeight="1">
+    <x:row r="136" ht="61.5" customHeight="1">
       <x:c r="A136" s="6" t="str">
         <x:v>d135</x:v>
       </x:c>
       <x:c r="B136" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C136" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2396,12 +2396,12 @@
       </x:c>
       <x:c r="E136" s="5" t="str"/>
     </x:row>
-    <x:row r="137" ht="51" customHeight="1">
+    <x:row r="137" ht="61.5" customHeight="1">
       <x:c r="A137" s="6" t="str">
         <x:v>d136</x:v>
       </x:c>
       <x:c r="B137" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C137" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2411,12 +2411,12 @@
       </x:c>
       <x:c r="E137" s="5" t="str"/>
     </x:row>
-    <x:row r="138" ht="51" customHeight="1">
+    <x:row r="138" ht="61.5" customHeight="1">
       <x:c r="A138" s="6" t="str">
         <x:v>d137</x:v>
       </x:c>
       <x:c r="B138" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C138" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2426,12 +2426,12 @@
       </x:c>
       <x:c r="E138" s="5" t="str"/>
     </x:row>
-    <x:row r="139" ht="51" customHeight="1">
+    <x:row r="139" ht="61.5" customHeight="1">
       <x:c r="A139" s="6" t="str">
         <x:v>d138</x:v>
       </x:c>
       <x:c r="B139" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C139" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2442,12 +2442,12 @@
       </x:c>
       <x:c r="E139" s="5" t="str"/>
     </x:row>
-    <x:row r="140" ht="51" customHeight="1">
+    <x:row r="140" ht="61.5" customHeight="1">
       <x:c r="A140" s="6" t="str">
         <x:v>d139</x:v>
       </x:c>
       <x:c r="B140" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C140" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2457,12 +2457,12 @@
       </x:c>
       <x:c r="E140" s="5" t="str"/>
     </x:row>
-    <x:row r="141" ht="51" customHeight="1">
+    <x:row r="141" ht="61.5" customHeight="1">
       <x:c r="A141" s="6" t="str">
         <x:v>d140</x:v>
       </x:c>
       <x:c r="B141" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C141" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2472,12 +2472,12 @@
       </x:c>
       <x:c r="E141" s="5" t="str"/>
     </x:row>
-    <x:row r="142" ht="51" customHeight="1">
+    <x:row r="142" ht="61.5" customHeight="1">
       <x:c r="A142" s="6" t="str">
         <x:v>d141</x:v>
       </x:c>
       <x:c r="B142" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C142" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2487,12 +2487,12 @@
       </x:c>
       <x:c r="E142" s="5" t="str"/>
     </x:row>
-    <x:row r="143" ht="51" customHeight="1">
+    <x:row r="143" ht="61.5" customHeight="1">
       <x:c r="A143" s="6" t="str">
         <x:v>d142</x:v>
       </x:c>
       <x:c r="B143" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C143" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2502,12 +2502,12 @@
       </x:c>
       <x:c r="E143" s="5" t="str"/>
     </x:row>
-    <x:row r="144" ht="51" customHeight="1">
+    <x:row r="144" ht="61.5" customHeight="1">
       <x:c r="A144" s="6" t="str">
         <x:v>d143</x:v>
       </x:c>
       <x:c r="B144" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C144" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2518,12 +2518,12 @@
       </x:c>
       <x:c r="E144" s="5" t="str"/>
     </x:row>
-    <x:row r="145" ht="51" customHeight="1">
+    <x:row r="145" ht="61.5" customHeight="1">
       <x:c r="A145" s="6" t="str">
         <x:v>d144</x:v>
       </x:c>
       <x:c r="B145" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C145" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2533,12 +2533,12 @@
       </x:c>
       <x:c r="E145" s="5" t="str"/>
     </x:row>
-    <x:row r="146" ht="51" customHeight="1">
+    <x:row r="146" ht="61.5" customHeight="1">
       <x:c r="A146" s="6" t="str">
         <x:v>d145</x:v>
       </x:c>
       <x:c r="B146" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C146" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2548,12 +2548,12 @@
       </x:c>
       <x:c r="E146" s="5" t="str"/>
     </x:row>
-    <x:row r="147" ht="51" customHeight="1">
+    <x:row r="147" ht="61.5" customHeight="1">
       <x:c r="A147" s="6" t="str">
         <x:v>d146</x:v>
       </x:c>
       <x:c r="B147" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C147" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2563,12 +2563,12 @@
       </x:c>
       <x:c r="E147" s="5" t="str"/>
     </x:row>
-    <x:row r="148" ht="51" customHeight="1">
+    <x:row r="148" ht="61.5" customHeight="1">
       <x:c r="A148" s="6" t="str">
         <x:v>d147</x:v>
       </x:c>
       <x:c r="B148" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C148" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2578,12 +2578,12 @@
       </x:c>
       <x:c r="E148" s="5" t="str"/>
     </x:row>
-    <x:row r="149" ht="51" customHeight="1">
+    <x:row r="149" ht="61.5" customHeight="1">
       <x:c r="A149" s="6" t="str">
         <x:v>d148</x:v>
       </x:c>
       <x:c r="B149" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C149" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2594,12 +2594,12 @@
       </x:c>
       <x:c r="E149" s="5" t="str"/>
     </x:row>
-    <x:row r="150" ht="51" customHeight="1">
+    <x:row r="150" ht="61.5" customHeight="1">
       <x:c r="A150" s="6" t="str">
         <x:v>d149</x:v>
       </x:c>
       <x:c r="B150" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C150" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2609,12 +2609,12 @@
       </x:c>
       <x:c r="E150" s="5" t="str"/>
     </x:row>
-    <x:row r="151" ht="51" customHeight="1">
+    <x:row r="151" ht="61.5" customHeight="1">
       <x:c r="A151" s="6" t="str">
         <x:v>d150</x:v>
       </x:c>
       <x:c r="B151" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C151" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2624,12 +2624,12 @@
       </x:c>
       <x:c r="E151" s="5" t="str"/>
     </x:row>
-    <x:row r="152" ht="51" customHeight="1">
+    <x:row r="152" ht="61.5" customHeight="1">
       <x:c r="A152" s="6" t="str">
         <x:v>d151</x:v>
       </x:c>
       <x:c r="B152" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C152" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2639,12 +2639,12 @@
       </x:c>
       <x:c r="E152" s="5" t="str"/>
     </x:row>
-    <x:row r="153" ht="51" customHeight="1">
+    <x:row r="153" ht="61.5" customHeight="1">
       <x:c r="A153" s="6" t="str">
         <x:v>d152</x:v>
       </x:c>
       <x:c r="B153" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C153" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2654,12 +2654,12 @@
       </x:c>
       <x:c r="E153" s="5" t="str"/>
     </x:row>
-    <x:row r="154" ht="51" customHeight="1">
+    <x:row r="154" ht="61.5" customHeight="1">
       <x:c r="A154" s="6" t="str">
         <x:v>d153</x:v>
       </x:c>
       <x:c r="B154" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C154" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2670,12 +2670,12 @@
       </x:c>
       <x:c r="E154" s="5" t="str"/>
     </x:row>
-    <x:row r="155" ht="51" customHeight="1">
+    <x:row r="155" ht="61.5" customHeight="1">
       <x:c r="A155" s="6" t="str">
         <x:v>d154</x:v>
       </x:c>
       <x:c r="B155" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C155" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2685,12 +2685,12 @@
       </x:c>
       <x:c r="E155" s="5" t="str"/>
     </x:row>
-    <x:row r="156" ht="51" customHeight="1">
+    <x:row r="156" ht="61.5" customHeight="1">
       <x:c r="A156" s="6" t="str">
         <x:v>d155</x:v>
       </x:c>
       <x:c r="B156" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C156" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2700,12 +2700,12 @@
       </x:c>
       <x:c r="E156" s="5" t="str"/>
     </x:row>
-    <x:row r="157" ht="51" customHeight="1">
+    <x:row r="157" ht="61.5" customHeight="1">
       <x:c r="A157" s="6" t="str">
         <x:v>d156</x:v>
       </x:c>
       <x:c r="B157" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C157" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2715,12 +2715,12 @@
       </x:c>
       <x:c r="E157" s="5" t="str"/>
     </x:row>
-    <x:row r="158" ht="51" customHeight="1">
+    <x:row r="158" ht="61.5" customHeight="1">
       <x:c r="A158" s="6" t="str">
         <x:v>d157</x:v>
       </x:c>
       <x:c r="B158" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C158" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2730,12 +2730,12 @@
       </x:c>
       <x:c r="E158" s="5" t="str"/>
     </x:row>
-    <x:row r="159" ht="51" customHeight="1">
+    <x:row r="159" ht="61.5" customHeight="1">
       <x:c r="A159" s="6" t="str">
         <x:v>d158</x:v>
       </x:c>
       <x:c r="B159" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C159" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2746,12 +2746,12 @@
       </x:c>
       <x:c r="E159" s="5" t="str"/>
     </x:row>
-    <x:row r="160" ht="51" customHeight="1">
+    <x:row r="160" ht="61.5" customHeight="1">
       <x:c r="A160" s="6" t="str">
         <x:v>d159</x:v>
       </x:c>
       <x:c r="B160" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C160" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2761,12 +2761,12 @@
       </x:c>
       <x:c r="E160" s="5" t="str"/>
     </x:row>
-    <x:row r="161" ht="51" customHeight="1">
+    <x:row r="161" ht="61.5" customHeight="1">
       <x:c r="A161" s="6" t="str">
         <x:v>d160</x:v>
       </x:c>
       <x:c r="B161" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C161" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2776,12 +2776,12 @@
       </x:c>
       <x:c r="E161" s="5" t="str"/>
     </x:row>
-    <x:row r="162" ht="51" customHeight="1">
+    <x:row r="162" ht="61.5" customHeight="1">
       <x:c r="A162" s="6" t="str">
         <x:v>d161</x:v>
       </x:c>
       <x:c r="B162" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C162" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2791,12 +2791,12 @@
       </x:c>
       <x:c r="E162" s="5" t="str"/>
     </x:row>
-    <x:row r="163" ht="51" customHeight="1">
+    <x:row r="163" ht="61.5" customHeight="1">
       <x:c r="A163" s="6" t="str">
         <x:v>d162</x:v>
       </x:c>
       <x:c r="B163" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C163" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2806,12 +2806,12 @@
       </x:c>
       <x:c r="E163" s="5" t="str"/>
     </x:row>
-    <x:row r="164" ht="51" customHeight="1">
+    <x:row r="164" ht="61.5" customHeight="1">
       <x:c r="A164" s="6" t="str">
         <x:v>d163</x:v>
       </x:c>
       <x:c r="B164" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C164" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2822,12 +2822,12 @@
       </x:c>
       <x:c r="E164" s="5" t="str"/>
     </x:row>
-    <x:row r="165" ht="51" customHeight="1">
+    <x:row r="165" ht="61.5" customHeight="1">
       <x:c r="A165" s="6" t="str">
         <x:v>d164</x:v>
       </x:c>
       <x:c r="B165" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C165" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2837,12 +2837,12 @@
       </x:c>
       <x:c r="E165" s="5" t="str"/>
     </x:row>
-    <x:row r="166" ht="51" customHeight="1">
+    <x:row r="166" ht="61.5" customHeight="1">
       <x:c r="A166" s="6" t="str">
         <x:v>d165</x:v>
       </x:c>
       <x:c r="B166" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C166" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2852,12 +2852,12 @@
       </x:c>
       <x:c r="E166" s="5" t="str"/>
     </x:row>
-    <x:row r="167" ht="51" customHeight="1">
+    <x:row r="167" ht="61.5" customHeight="1">
       <x:c r="A167" s="6" t="str">
         <x:v>d166</x:v>
       </x:c>
       <x:c r="B167" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C167" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2867,12 +2867,12 @@
       </x:c>
       <x:c r="E167" s="5" t="str"/>
     </x:row>
-    <x:row r="168" ht="51" customHeight="1">
+    <x:row r="168" ht="61.5" customHeight="1">
       <x:c r="A168" s="6" t="str">
         <x:v>d167</x:v>
       </x:c>
       <x:c r="B168" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C168" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2882,12 +2882,12 @@
       </x:c>
       <x:c r="E168" s="5" t="str"/>
     </x:row>
-    <x:row r="169" ht="51" customHeight="1">
+    <x:row r="169" ht="61.5" customHeight="1">
       <x:c r="A169" s="6" t="str">
         <x:v>d168</x:v>
       </x:c>
       <x:c r="B169" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C169" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2898,12 +2898,12 @@
       </x:c>
       <x:c r="E169" s="5" t="str"/>
     </x:row>
-    <x:row r="170" ht="51" customHeight="1">
+    <x:row r="170" ht="61.5" customHeight="1">
       <x:c r="A170" s="6" t="str">
         <x:v>d169</x:v>
       </x:c>
       <x:c r="B170" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C170" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2913,12 +2913,12 @@
       </x:c>
       <x:c r="E170" s="5" t="str"/>
     </x:row>
-    <x:row r="171" ht="51" customHeight="1">
+    <x:row r="171" ht="61.5" customHeight="1">
       <x:c r="A171" s="6" t="str">
         <x:v>d170</x:v>
       </x:c>
       <x:c r="B171" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C171" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2928,12 +2928,12 @@
       </x:c>
       <x:c r="E171" s="5" t="str"/>
     </x:row>
-    <x:row r="172" ht="51" customHeight="1">
+    <x:row r="172" ht="61.5" customHeight="1">
       <x:c r="A172" s="6" t="str">
         <x:v>d171</x:v>
       </x:c>
       <x:c r="B172" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C172" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2943,12 +2943,12 @@
       </x:c>
       <x:c r="E172" s="5" t="str"/>
     </x:row>
-    <x:row r="173" ht="51" customHeight="1">
+    <x:row r="173" ht="61.5" customHeight="1">
       <x:c r="A173" s="6" t="str">
         <x:v>d172</x:v>
       </x:c>
       <x:c r="B173" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C173" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2958,12 +2958,12 @@
       </x:c>
       <x:c r="E173" s="5" t="str"/>
     </x:row>
-    <x:row r="174" ht="51" customHeight="1">
+    <x:row r="174" ht="61.5" customHeight="1">
       <x:c r="A174" s="6" t="str">
         <x:v>d173</x:v>
       </x:c>
       <x:c r="B174" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C174" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -2974,12 +2974,12 @@
       </x:c>
       <x:c r="E174" s="5" t="str"/>
     </x:row>
-    <x:row r="175" ht="51" customHeight="1">
+    <x:row r="175" ht="61.5" customHeight="1">
       <x:c r="A175" s="6" t="str">
         <x:v>d174</x:v>
       </x:c>
       <x:c r="B175" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C175" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -2989,12 +2989,12 @@
       </x:c>
       <x:c r="E175" s="5" t="str"/>
     </x:row>
-    <x:row r="176" ht="51" customHeight="1">
+    <x:row r="176" ht="61.5" customHeight="1">
       <x:c r="A176" s="6" t="str">
         <x:v>d175</x:v>
       </x:c>
       <x:c r="B176" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C176" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3004,12 +3004,12 @@
       </x:c>
       <x:c r="E176" s="5" t="str"/>
     </x:row>
-    <x:row r="177" ht="51" customHeight="1">
+    <x:row r="177" ht="61.5" customHeight="1">
       <x:c r="A177" s="6" t="str">
         <x:v>d176</x:v>
       </x:c>
       <x:c r="B177" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C177" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3019,12 +3019,12 @@
       </x:c>
       <x:c r="E177" s="5" t="str"/>
     </x:row>
-    <x:row r="178" ht="51" customHeight="1">
+    <x:row r="178" ht="61.5" customHeight="1">
       <x:c r="A178" s="6" t="str">
         <x:v>d177</x:v>
       </x:c>
       <x:c r="B178" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C178" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3035,12 +3035,12 @@
       </x:c>
       <x:c r="E178" s="5" t="str"/>
     </x:row>
-    <x:row r="179" ht="51" customHeight="1">
+    <x:row r="179" ht="61.5" customHeight="1">
       <x:c r="A179" s="6" t="str">
         <x:v>d178</x:v>
       </x:c>
       <x:c r="B179" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C179" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3050,12 +3050,12 @@
       </x:c>
       <x:c r="E179" s="5" t="str"/>
     </x:row>
-    <x:row r="180" ht="51" customHeight="1">
+    <x:row r="180" ht="61.5" customHeight="1">
       <x:c r="A180" s="6" t="str">
         <x:v>d179</x:v>
       </x:c>
       <x:c r="B180" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C180" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3065,12 +3065,12 @@
       </x:c>
       <x:c r="E180" s="5" t="str"/>
     </x:row>
-    <x:row r="181" ht="51" customHeight="1">
+    <x:row r="181" ht="61.5" customHeight="1">
       <x:c r="A181" s="6" t="str">
         <x:v>d180</x:v>
       </x:c>
       <x:c r="B181" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C181" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3080,12 +3080,12 @@
       </x:c>
       <x:c r="E181" s="5" t="str"/>
     </x:row>
-    <x:row r="182" ht="51" customHeight="1">
+    <x:row r="182" ht="61.5" customHeight="1">
       <x:c r="A182" s="6" t="str">
         <x:v>d181</x:v>
       </x:c>
       <x:c r="B182" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C182" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3095,12 +3095,12 @@
       </x:c>
       <x:c r="E182" s="5" t="str"/>
     </x:row>
-    <x:row r="183" ht="51" customHeight="1">
+    <x:row r="183" ht="61.5" customHeight="1">
       <x:c r="A183" s="6" t="str">
         <x:v>d182</x:v>
       </x:c>
       <x:c r="B183" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C183" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3111,12 +3111,12 @@
       </x:c>
       <x:c r="E183" s="5" t="str"/>
     </x:row>
-    <x:row r="184" ht="51" customHeight="1">
+    <x:row r="184" ht="61.5" customHeight="1">
       <x:c r="A184" s="6" t="str">
         <x:v>d183</x:v>
       </x:c>
       <x:c r="B184" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C184" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3126,12 +3126,12 @@
       </x:c>
       <x:c r="E184" s="5" t="str"/>
     </x:row>
-    <x:row r="185" ht="51" customHeight="1">
+    <x:row r="185" ht="61.5" customHeight="1">
       <x:c r="A185" s="6" t="str">
         <x:v>d184</x:v>
       </x:c>
       <x:c r="B185" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C185" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3141,12 +3141,12 @@
       </x:c>
       <x:c r="E185" s="5" t="str"/>
     </x:row>
-    <x:row r="186" ht="51" customHeight="1">
+    <x:row r="186" ht="61.5" customHeight="1">
       <x:c r="A186" s="6" t="str">
         <x:v>d185</x:v>
       </x:c>
       <x:c r="B186" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C186" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3156,12 +3156,12 @@
       </x:c>
       <x:c r="E186" s="5" t="str"/>
     </x:row>
-    <x:row r="187" ht="51" customHeight="1">
+    <x:row r="187" ht="61.5" customHeight="1">
       <x:c r="A187" s="6" t="str">
         <x:v>d186</x:v>
       </x:c>
       <x:c r="B187" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C187" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3171,12 +3171,12 @@
       </x:c>
       <x:c r="E187" s="5" t="str"/>
     </x:row>
-    <x:row r="188" ht="51" customHeight="1">
+    <x:row r="188" ht="61.5" customHeight="1">
       <x:c r="A188" s="6" t="str">
         <x:v>d187</x:v>
       </x:c>
       <x:c r="B188" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C188" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3187,12 +3187,12 @@
       </x:c>
       <x:c r="E188" s="5" t="str"/>
     </x:row>
-    <x:row r="189" ht="51" customHeight="1">
+    <x:row r="189" ht="61.5" customHeight="1">
       <x:c r="A189" s="6" t="str">
         <x:v>d188</x:v>
       </x:c>
       <x:c r="B189" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C189" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3202,12 +3202,12 @@
       </x:c>
       <x:c r="E189" s="5" t="str"/>
     </x:row>
-    <x:row r="190" ht="51" customHeight="1">
+    <x:row r="190" ht="61.5" customHeight="1">
       <x:c r="A190" s="6" t="str">
         <x:v>d189</x:v>
       </x:c>
       <x:c r="B190" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C190" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3217,12 +3217,12 @@
       </x:c>
       <x:c r="E190" s="5" t="str"/>
     </x:row>
-    <x:row r="191" ht="51" customHeight="1">
+    <x:row r="191" ht="61.5" customHeight="1">
       <x:c r="A191" s="6" t="str">
         <x:v>d190</x:v>
       </x:c>
       <x:c r="B191" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C191" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3232,12 +3232,12 @@
       </x:c>
       <x:c r="E191" s="5" t="str"/>
     </x:row>
-    <x:row r="192" ht="51" customHeight="1">
+    <x:row r="192" ht="61.5" customHeight="1">
       <x:c r="A192" s="6" t="str">
         <x:v>d191</x:v>
       </x:c>
       <x:c r="B192" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C192" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3248,12 +3248,12 @@
       </x:c>
       <x:c r="E192" s="5" t="str"/>
     </x:row>
-    <x:row r="193" ht="51" customHeight="1">
+    <x:row r="193" ht="61.5" customHeight="1">
       <x:c r="A193" s="6" t="str">
         <x:v>d192</x:v>
       </x:c>
       <x:c r="B193" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C193" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3263,12 +3263,12 @@
       </x:c>
       <x:c r="E193" s="5" t="str"/>
     </x:row>
-    <x:row r="194" ht="51" customHeight="1">
+    <x:row r="194" ht="61.5" customHeight="1">
       <x:c r="A194" s="6" t="str">
         <x:v>d193</x:v>
       </x:c>
       <x:c r="B194" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C194" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3278,12 +3278,12 @@
       </x:c>
       <x:c r="E194" s="5" t="str"/>
     </x:row>
-    <x:row r="195" ht="51" customHeight="1">
+    <x:row r="195" ht="61.5" customHeight="1">
       <x:c r="A195" s="6" t="str">
         <x:v>d194</x:v>
       </x:c>
       <x:c r="B195" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C195" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3293,12 +3293,12 @@
       </x:c>
       <x:c r="E195" s="5" t="str"/>
     </x:row>
-    <x:row r="196" ht="51" customHeight="1">
+    <x:row r="196" ht="61.5" customHeight="1">
       <x:c r="A196" s="6" t="str">
         <x:v>d195</x:v>
       </x:c>
       <x:c r="B196" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C196" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3308,12 +3308,12 @@
       </x:c>
       <x:c r="E196" s="5" t="str"/>
     </x:row>
-    <x:row r="197" ht="51" customHeight="1">
+    <x:row r="197" ht="61.5" customHeight="1">
       <x:c r="A197" s="6" t="str">
         <x:v>d196</x:v>
       </x:c>
       <x:c r="B197" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C197" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3324,12 +3324,12 @@
       </x:c>
       <x:c r="E197" s="5" t="str"/>
     </x:row>
-    <x:row r="198" ht="51" customHeight="1">
+    <x:row r="198" ht="61.5" customHeight="1">
       <x:c r="A198" s="6" t="str">
         <x:v>d197</x:v>
       </x:c>
       <x:c r="B198" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C198" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3339,12 +3339,12 @@
       </x:c>
       <x:c r="E198" s="5" t="str"/>
     </x:row>
-    <x:row r="199" ht="51" customHeight="1">
+    <x:row r="199" ht="61.5" customHeight="1">
       <x:c r="A199" s="6" t="str">
         <x:v>d198</x:v>
       </x:c>
       <x:c r="B199" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C199" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3354,12 +3354,12 @@
       </x:c>
       <x:c r="E199" s="5" t="str"/>
     </x:row>
-    <x:row r="200" ht="51" customHeight="1">
+    <x:row r="200" ht="61.5" customHeight="1">
       <x:c r="A200" s="6" t="str">
         <x:v>d199</x:v>
       </x:c>
       <x:c r="B200" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C200" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3369,12 +3369,12 @@
       </x:c>
       <x:c r="E200" s="5" t="str"/>
     </x:row>
-    <x:row r="201" ht="51" customHeight="1">
+    <x:row r="201" ht="61.5" customHeight="1">
       <x:c r="A201" s="6" t="str">
         <x:v>d200</x:v>
       </x:c>
       <x:c r="B201" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C201" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3384,12 +3384,12 @@
       </x:c>
       <x:c r="E201" s="5" t="str"/>
     </x:row>
-    <x:row r="202" ht="51" customHeight="1">
+    <x:row r="202" ht="61.5" customHeight="1">
       <x:c r="A202" s="6" t="str">
         <x:v>d201</x:v>
       </x:c>
       <x:c r="B202" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C202" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3400,12 +3400,12 @@
       </x:c>
       <x:c r="E202" s="5" t="str"/>
     </x:row>
-    <x:row r="203" ht="51" customHeight="1">
+    <x:row r="203" ht="61.5" customHeight="1">
       <x:c r="A203" s="6" t="str">
         <x:v>d202</x:v>
       </x:c>
       <x:c r="B203" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C203" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3415,12 +3415,12 @@
       </x:c>
       <x:c r="E203" s="5" t="str"/>
     </x:row>
-    <x:row r="204" ht="57.75" customHeight="1">
+    <x:row r="204" ht="61.5" customHeight="1">
       <x:c r="A204" s="6" t="str">
         <x:v>d203</x:v>
       </x:c>
       <x:c r="B204" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C204" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3430,12 +3430,12 @@
       </x:c>
       <x:c r="E204" s="5" t="str"/>
     </x:row>
-    <x:row r="205" ht="51" customHeight="1">
+    <x:row r="205" ht="61.5" customHeight="1">
       <x:c r="A205" s="6" t="str">
         <x:v>d204</x:v>
       </x:c>
       <x:c r="B205" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C205" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3445,12 +3445,12 @@
       </x:c>
       <x:c r="E205" s="5" t="str"/>
     </x:row>
-    <x:row r="206" ht="51" customHeight="1">
+    <x:row r="206" ht="61.5" customHeight="1">
       <x:c r="A206" s="6" t="str">
         <x:v>d205</x:v>
       </x:c>
       <x:c r="B206" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C206" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3460,12 +3460,12 @@
       </x:c>
       <x:c r="E206" s="5" t="str"/>
     </x:row>
-    <x:row r="207" ht="51" customHeight="1">
+    <x:row r="207" ht="61.5" customHeight="1">
       <x:c r="A207" s="6" t="str">
         <x:v>d206</x:v>
       </x:c>
       <x:c r="B207" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C207" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3476,12 +3476,12 @@
       </x:c>
       <x:c r="E207" s="5" t="str"/>
     </x:row>
-    <x:row r="208" ht="51" customHeight="1">
+    <x:row r="208" ht="61.5" customHeight="1">
       <x:c r="A208" s="6" t="str">
         <x:v>d207</x:v>
       </x:c>
       <x:c r="B208" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C208" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3491,12 +3491,12 @@
       </x:c>
       <x:c r="E208" s="5" t="str"/>
     </x:row>
-    <x:row r="209" ht="51" customHeight="1">
+    <x:row r="209" ht="61.5" customHeight="1">
       <x:c r="A209" s="6" t="str">
         <x:v>d208</x:v>
       </x:c>
       <x:c r="B209" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C209" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3506,12 +3506,12 @@
       </x:c>
       <x:c r="E209" s="5" t="str"/>
     </x:row>
-    <x:row r="210" ht="57.75" customHeight="1">
+    <x:row r="210" ht="61.5" customHeight="1">
       <x:c r="A210" s="6" t="str">
         <x:v>d209</x:v>
       </x:c>
       <x:c r="B210" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C210" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3521,12 +3521,12 @@
       </x:c>
       <x:c r="E210" s="5" t="str"/>
     </x:row>
-    <x:row r="211" ht="57.75" customHeight="1">
+    <x:row r="211" ht="61.5" customHeight="1">
       <x:c r="A211" s="6" t="str">
         <x:v>d210</x:v>
       </x:c>
       <x:c r="B211" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C211" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3541,7 +3541,7 @@
         <x:v>d211</x:v>
       </x:c>
       <x:c r="B212" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C212" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3557,7 +3557,7 @@
         <x:v>d212</x:v>
       </x:c>
       <x:c r="B213" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C213" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3567,12 +3567,12 @@
       </x:c>
       <x:c r="E213" s="5" t="str"/>
     </x:row>
-    <x:row r="214" ht="57.75" customHeight="1">
+    <x:row r="214" ht="61.5" customHeight="1">
       <x:c r="A214" s="6" t="str">
         <x:v>d213</x:v>
       </x:c>
       <x:c r="B214" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C214" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3587,7 +3587,7 @@
         <x:v>d214</x:v>
       </x:c>
       <x:c r="B215" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C215" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3597,12 +3597,12 @@
       </x:c>
       <x:c r="E215" s="5" t="str"/>
     </x:row>
-    <x:row r="216" ht="57.75" customHeight="1">
+    <x:row r="216" ht="61.5" customHeight="1">
       <x:c r="A216" s="6" t="str">
         <x:v>d215</x:v>
       </x:c>
       <x:c r="B216" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C216" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3612,12 +3612,12 @@
       </x:c>
       <x:c r="E216" s="5" t="str"/>
     </x:row>
-    <x:row r="217" ht="57.75" customHeight="1">
+    <x:row r="217" ht="61.5" customHeight="1">
       <x:c r="A217" s="6" t="str">
         <x:v>d216</x:v>
       </x:c>
       <x:c r="B217" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C217" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3628,12 +3628,12 @@
       </x:c>
       <x:c r="E217" s="5" t="str"/>
     </x:row>
-    <x:row r="218" ht="57.75" customHeight="1">
+    <x:row r="218" ht="61.5" customHeight="1">
       <x:c r="A218" s="6" t="str">
         <x:v>d217</x:v>
       </x:c>
       <x:c r="B218" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C218" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3648,7 +3648,7 @@
         <x:v>d218</x:v>
       </x:c>
       <x:c r="B219" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C219" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3663,7 +3663,7 @@
         <x:v>d219</x:v>
       </x:c>
       <x:c r="B220" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C220" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3678,7 +3678,7 @@
         <x:v>d220</x:v>
       </x:c>
       <x:c r="B221" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C221" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3693,7 +3693,7 @@
         <x:v>d221</x:v>
       </x:c>
       <x:c r="B222" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C222" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3709,7 +3709,7 @@
         <x:v>d222</x:v>
       </x:c>
       <x:c r="B223" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C223" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3719,12 +3719,12 @@
       </x:c>
       <x:c r="E223" s="5" t="str"/>
     </x:row>
-    <x:row r="224" ht="57.75" customHeight="1">
+    <x:row r="224" ht="61.5" customHeight="1">
       <x:c r="A224" s="6" t="str">
         <x:v>d223</x:v>
       </x:c>
       <x:c r="B224" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C224" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3734,12 +3734,12 @@
       </x:c>
       <x:c r="E224" s="5" t="str"/>
     </x:row>
-    <x:row r="225" ht="51" customHeight="1">
+    <x:row r="225" ht="61.5" customHeight="1">
       <x:c r="A225" s="6" t="str">
         <x:v>d224</x:v>
       </x:c>
       <x:c r="B225" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C225" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3749,12 +3749,12 @@
       </x:c>
       <x:c r="E225" s="5" t="str"/>
     </x:row>
-    <x:row r="226" ht="57.75" customHeight="1">
+    <x:row r="226" ht="61.5" customHeight="1">
       <x:c r="A226" s="6" t="str">
         <x:v>d225</x:v>
       </x:c>
       <x:c r="B226" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C226" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3764,12 +3764,12 @@
       </x:c>
       <x:c r="E226" s="5" t="str"/>
     </x:row>
-    <x:row r="227" ht="57.75" customHeight="1">
+    <x:row r="227" ht="61.5" customHeight="1">
       <x:c r="A227" s="6" t="str">
         <x:v>d226</x:v>
       </x:c>
       <x:c r="B227" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C227" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3780,12 +3780,12 @@
       </x:c>
       <x:c r="E227" s="5" t="str"/>
     </x:row>
-    <x:row r="228" ht="57.75" customHeight="1">
+    <x:row r="228" ht="61.5" customHeight="1">
       <x:c r="A228" s="6" t="str">
         <x:v>d227</x:v>
       </x:c>
       <x:c r="B228" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C228" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3795,12 +3795,12 @@
       </x:c>
       <x:c r="E228" s="5" t="str"/>
     </x:row>
-    <x:row r="229" ht="57.75" customHeight="1">
+    <x:row r="229" ht="61.5" customHeight="1">
       <x:c r="A229" s="6" t="str">
         <x:v>d228</x:v>
       </x:c>
       <x:c r="B229" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C229" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3815,7 +3815,7 @@
         <x:v>d229</x:v>
       </x:c>
       <x:c r="B230" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C230" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3830,7 +3830,7 @@
         <x:v>d230</x:v>
       </x:c>
       <x:c r="B231" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C231" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3841,12 +3841,12 @@
       </x:c>
       <x:c r="E231" s="5" t="str"/>
     </x:row>
-    <x:row r="232" ht="57.75" customHeight="1">
+    <x:row r="232" ht="61.5" customHeight="1">
       <x:c r="A232" s="6" t="str">
         <x:v>d231</x:v>
       </x:c>
       <x:c r="B232" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C232" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3856,12 +3856,12 @@
       </x:c>
       <x:c r="E232" s="5" t="str"/>
     </x:row>
-    <x:row r="233" ht="57.75" customHeight="1">
+    <x:row r="233" ht="61.5" customHeight="1">
       <x:c r="A233" s="6" t="str">
         <x:v>d232</x:v>
       </x:c>
       <x:c r="B233" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C233" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3876,7 +3876,7 @@
         <x:v>d233</x:v>
       </x:c>
       <x:c r="B234" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C234" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3886,12 +3886,12 @@
       </x:c>
       <x:c r="E234" s="5" t="str"/>
     </x:row>
-    <x:row r="235" ht="57.75" customHeight="1">
+    <x:row r="235" ht="61.5" customHeight="1">
       <x:c r="A235" s="6" t="str">
         <x:v>d234</x:v>
       </x:c>
       <x:c r="B235" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C235" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3901,12 +3901,12 @@
       </x:c>
       <x:c r="E235" s="5" t="str"/>
     </x:row>
-    <x:row r="236" ht="57.75" customHeight="1">
+    <x:row r="236" ht="61.5" customHeight="1">
       <x:c r="A236" s="6" t="str">
         <x:v>d235</x:v>
       </x:c>
       <x:c r="B236" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C236" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3917,12 +3917,12 @@
       </x:c>
       <x:c r="E236" s="5" t="str"/>
     </x:row>
-    <x:row r="237" ht="57.75" customHeight="1">
+    <x:row r="237" ht="61.5" customHeight="1">
       <x:c r="A237" s="6" t="str">
         <x:v>d236</x:v>
       </x:c>
       <x:c r="B237" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C237" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3932,12 +3932,12 @@
       </x:c>
       <x:c r="E237" s="5" t="str"/>
     </x:row>
-    <x:row r="238" ht="57.75" customHeight="1">
+    <x:row r="238" ht="61.5" customHeight="1">
       <x:c r="A238" s="6" t="str">
         <x:v>d237</x:v>
       </x:c>
       <x:c r="B238" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C238" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3947,12 +3947,12 @@
       </x:c>
       <x:c r="E238" s="5" t="str"/>
     </x:row>
-    <x:row r="239" ht="57.75" customHeight="1">
+    <x:row r="239" ht="61.5" customHeight="1">
       <x:c r="A239" s="6" t="str">
         <x:v>d238</x:v>
       </x:c>
       <x:c r="B239" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C239" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3962,12 +3962,12 @@
       </x:c>
       <x:c r="E239" s="5" t="str"/>
     </x:row>
-    <x:row r="240" ht="57.75" customHeight="1">
+    <x:row r="240" ht="61.5" customHeight="1">
       <x:c r="A240" s="6" t="str">
         <x:v>d239</x:v>
       </x:c>
       <x:c r="B240" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C240" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -3977,12 +3977,12 @@
       </x:c>
       <x:c r="E240" s="5" t="str"/>
     </x:row>
-    <x:row r="241" ht="57.75" customHeight="1">
+    <x:row r="241" ht="61.5" customHeight="1">
       <x:c r="A241" s="6" t="str">
         <x:v>d240</x:v>
       </x:c>
       <x:c r="B241" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C241" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -3993,12 +3993,12 @@
       </x:c>
       <x:c r="E241" s="5" t="str"/>
     </x:row>
-    <x:row r="242" ht="57.75" customHeight="1">
+    <x:row r="242" ht="61.5" customHeight="1">
       <x:c r="A242" s="6" t="str">
         <x:v>d241</x:v>
       </x:c>
       <x:c r="B242" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C242" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4008,12 +4008,12 @@
       </x:c>
       <x:c r="E242" s="5" t="str"/>
     </x:row>
-    <x:row r="243" ht="57.75" customHeight="1">
+    <x:row r="243" ht="61.5" customHeight="1">
       <x:c r="A243" s="6" t="str">
         <x:v>d242</x:v>
       </x:c>
       <x:c r="B243" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C243" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4023,12 +4023,12 @@
       </x:c>
       <x:c r="E243" s="5" t="str"/>
     </x:row>
-    <x:row r="244" ht="51" customHeight="1">
+    <x:row r="244" ht="61.5" customHeight="1">
       <x:c r="A244" s="6" t="str">
         <x:v>d243</x:v>
       </x:c>
       <x:c r="B244" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C244" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4038,12 +4038,12 @@
       </x:c>
       <x:c r="E244" s="5" t="str"/>
     </x:row>
-    <x:row r="245" ht="57.75" customHeight="1">
+    <x:row r="245" ht="61.5" customHeight="1">
       <x:c r="A245" s="6" t="str">
         <x:v>d244</x:v>
       </x:c>
       <x:c r="B245" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C245" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4054,12 +4054,12 @@
       </x:c>
       <x:c r="E245" s="5" t="str"/>
     </x:row>
-    <x:row r="246" ht="57.75" customHeight="1">
+    <x:row r="246" ht="61.5" customHeight="1">
       <x:c r="A246" s="6" t="str">
         <x:v>d245</x:v>
       </x:c>
       <x:c r="B246" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C246" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4069,12 +4069,12 @@
       </x:c>
       <x:c r="E246" s="5" t="str"/>
     </x:row>
-    <x:row r="247" ht="51" customHeight="1">
+    <x:row r="247" ht="61.5" customHeight="1">
       <x:c r="A247" s="6" t="str">
         <x:v>d246</x:v>
       </x:c>
       <x:c r="B247" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C247" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4084,12 +4084,12 @@
       </x:c>
       <x:c r="E247" s="5" t="str"/>
     </x:row>
-    <x:row r="248" ht="51" customHeight="1">
+    <x:row r="248" ht="61.5" customHeight="1">
       <x:c r="A248" s="6" t="str">
         <x:v>d247</x:v>
       </x:c>
       <x:c r="B248" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C248" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4099,12 +4099,12 @@
       </x:c>
       <x:c r="E248" s="5" t="str"/>
     </x:row>
-    <x:row r="249" ht="51" customHeight="1">
+    <x:row r="249" ht="61.5" customHeight="1">
       <x:c r="A249" s="6" t="str">
         <x:v>d248</x:v>
       </x:c>
       <x:c r="B249" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C249" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4114,12 +4114,12 @@
       </x:c>
       <x:c r="E249" s="5" t="str"/>
     </x:row>
-    <x:row r="250" ht="51" customHeight="1">
+    <x:row r="250" ht="61.5" customHeight="1">
       <x:c r="A250" s="6" t="str">
         <x:v>d249</x:v>
       </x:c>
       <x:c r="B250" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C250" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4130,12 +4130,12 @@
       </x:c>
       <x:c r="E250" s="5" t="str"/>
     </x:row>
-    <x:row r="251" ht="51" customHeight="1">
+    <x:row r="251" ht="61.5" customHeight="1">
       <x:c r="A251" s="6" t="str">
         <x:v>d250</x:v>
       </x:c>
       <x:c r="B251" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C251" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4145,12 +4145,12 @@
       </x:c>
       <x:c r="E251" s="5" t="str"/>
     </x:row>
-    <x:row r="252" ht="51" customHeight="1">
+    <x:row r="252" ht="61.5" customHeight="1">
       <x:c r="A252" s="6" t="str">
         <x:v>d251</x:v>
       </x:c>
       <x:c r="B252" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C252" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4160,12 +4160,12 @@
       </x:c>
       <x:c r="E252" s="5" t="str"/>
     </x:row>
-    <x:row r="253" ht="51" customHeight="1">
+    <x:row r="253" ht="61.5" customHeight="1">
       <x:c r="A253" s="6" t="str">
         <x:v>d252</x:v>
       </x:c>
       <x:c r="B253" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C253" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4175,12 +4175,12 @@
       </x:c>
       <x:c r="E253" s="5" t="str"/>
     </x:row>
-    <x:row r="254" ht="51" customHeight="1">
+    <x:row r="254" ht="61.5" customHeight="1">
       <x:c r="A254" s="6" t="str">
         <x:v>d253</x:v>
       </x:c>
       <x:c r="B254" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C254" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4190,12 +4190,12 @@
       </x:c>
       <x:c r="E254" s="5" t="str"/>
     </x:row>
-    <x:row r="255" ht="51" customHeight="1">
+    <x:row r="255" ht="61.5" customHeight="1">
       <x:c r="A255" s="6" t="str">
         <x:v>d254</x:v>
       </x:c>
       <x:c r="B255" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C255" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4206,12 +4206,12 @@
       </x:c>
       <x:c r="E255" s="5" t="str"/>
     </x:row>
-    <x:row r="256" ht="51" customHeight="1">
+    <x:row r="256" ht="61.5" customHeight="1">
       <x:c r="A256" s="6" t="str">
         <x:v>d255</x:v>
       </x:c>
       <x:c r="B256" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C256" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4221,12 +4221,12 @@
       </x:c>
       <x:c r="E256" s="5" t="str"/>
     </x:row>
-    <x:row r="257" ht="51" customHeight="1">
+    <x:row r="257" ht="61.5" customHeight="1">
       <x:c r="A257" s="6" t="str">
         <x:v>d256</x:v>
       </x:c>
       <x:c r="B257" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C257" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4236,12 +4236,12 @@
       </x:c>
       <x:c r="E257" s="5" t="str"/>
     </x:row>
-    <x:row r="258" ht="51" customHeight="1">
+    <x:row r="258" ht="61.5" customHeight="1">
       <x:c r="A258" s="6" t="str">
         <x:v>d257</x:v>
       </x:c>
       <x:c r="B258" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C258" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4251,12 +4251,12 @@
       </x:c>
       <x:c r="E258" s="5" t="str"/>
     </x:row>
-    <x:row r="259" ht="51" customHeight="1">
+    <x:row r="259" ht="61.5" customHeight="1">
       <x:c r="A259" s="6" t="str">
         <x:v>d258</x:v>
       </x:c>
       <x:c r="B259" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C259" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4266,12 +4266,12 @@
       </x:c>
       <x:c r="E259" s="5" t="str"/>
     </x:row>
-    <x:row r="260" ht="51" customHeight="1">
+    <x:row r="260" ht="61.5" customHeight="1">
       <x:c r="A260" s="6" t="str">
         <x:v>d259</x:v>
       </x:c>
       <x:c r="B260" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C260" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4282,12 +4282,12 @@
       </x:c>
       <x:c r="E260" s="5" t="str"/>
     </x:row>
-    <x:row r="261" ht="51" customHeight="1">
+    <x:row r="261" ht="61.5" customHeight="1">
       <x:c r="A261" s="6" t="str">
         <x:v>d260</x:v>
       </x:c>
       <x:c r="B261" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C261" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4297,12 +4297,12 @@
       </x:c>
       <x:c r="E261" s="5" t="str"/>
     </x:row>
-    <x:row r="262" ht="51" customHeight="1">
+    <x:row r="262" ht="61.5" customHeight="1">
       <x:c r="A262" s="6" t="str">
         <x:v>d261</x:v>
       </x:c>
       <x:c r="B262" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C262" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4312,12 +4312,12 @@
       </x:c>
       <x:c r="E262" s="5" t="str"/>
     </x:row>
-    <x:row r="263" ht="51" customHeight="1">
+    <x:row r="263" ht="61.5" customHeight="1">
       <x:c r="A263" s="6" t="str">
         <x:v>d262</x:v>
       </x:c>
       <x:c r="B263" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C263" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4327,12 +4327,12 @@
       </x:c>
       <x:c r="E263" s="5" t="str"/>
     </x:row>
-    <x:row r="264" ht="51" customHeight="1">
+    <x:row r="264" ht="61.5" customHeight="1">
       <x:c r="A264" s="6" t="str">
         <x:v>d263</x:v>
       </x:c>
       <x:c r="B264" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C264" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4342,12 +4342,12 @@
       </x:c>
       <x:c r="E264" s="5" t="str"/>
     </x:row>
-    <x:row r="265" ht="51" customHeight="1">
+    <x:row r="265" ht="61.5" customHeight="1">
       <x:c r="A265" s="6" t="str">
         <x:v>d264</x:v>
       </x:c>
       <x:c r="B265" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C265" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4358,12 +4358,12 @@
       </x:c>
       <x:c r="E265" s="5" t="str"/>
     </x:row>
-    <x:row r="266" ht="51" customHeight="1">
+    <x:row r="266" ht="61.5" customHeight="1">
       <x:c r="A266" s="6" t="str">
         <x:v>d265</x:v>
       </x:c>
       <x:c r="B266" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C266" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4373,12 +4373,12 @@
       </x:c>
       <x:c r="E266" s="5" t="str"/>
     </x:row>
-    <x:row r="267" ht="51" customHeight="1">
+    <x:row r="267" ht="61.5" customHeight="1">
       <x:c r="A267" s="6" t="str">
         <x:v>d266</x:v>
       </x:c>
       <x:c r="B267" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C267" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4388,12 +4388,12 @@
       </x:c>
       <x:c r="E267" s="5" t="str"/>
     </x:row>
-    <x:row r="268" ht="51" customHeight="1">
+    <x:row r="268" ht="61.5" customHeight="1">
       <x:c r="A268" s="6" t="str">
         <x:v>d267</x:v>
       </x:c>
       <x:c r="B268" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C268" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4403,12 +4403,12 @@
       </x:c>
       <x:c r="E268" s="5" t="str"/>
     </x:row>
-    <x:row r="269" ht="51" customHeight="1">
+    <x:row r="269" ht="61.5" customHeight="1">
       <x:c r="A269" s="6" t="str">
         <x:v>d268</x:v>
       </x:c>
       <x:c r="B269" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C269" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4418,12 +4418,12 @@
       </x:c>
       <x:c r="E269" s="5" t="str"/>
     </x:row>
-    <x:row r="270" ht="51" customHeight="1">
+    <x:row r="270" ht="61.5" customHeight="1">
       <x:c r="A270" s="6" t="str">
         <x:v>d269</x:v>
       </x:c>
       <x:c r="B270" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C270" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4434,12 +4434,12 @@
       </x:c>
       <x:c r="E270" s="5" t="str"/>
     </x:row>
-    <x:row r="271" ht="51" customHeight="1">
+    <x:row r="271" ht="61.5" customHeight="1">
       <x:c r="A271" s="6" t="str">
         <x:v>d270</x:v>
       </x:c>
       <x:c r="B271" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C271" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4454,7 +4454,7 @@
         <x:v>d271</x:v>
       </x:c>
       <x:c r="B272" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C272" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4469,7 +4469,7 @@
         <x:v>d272</x:v>
       </x:c>
       <x:c r="B273" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C273" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4484,7 +4484,7 @@
         <x:v>d273</x:v>
       </x:c>
       <x:c r="B274" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C274" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4499,7 +4499,7 @@
         <x:v>d274</x:v>
       </x:c>
       <x:c r="B275" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C275" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4514,7 +4514,7 @@
         <x:v>d275</x:v>
       </x:c>
       <x:c r="B276" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C276" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4529,7 +4529,7 @@
         <x:v>d276</x:v>
       </x:c>
       <x:c r="B277" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C277" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4544,7 +4544,7 @@
         <x:v>d277</x:v>
       </x:c>
       <x:c r="B278" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C278" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4561,7 +4561,7 @@
         <x:v>d278</x:v>
       </x:c>
       <x:c r="B279" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C279" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4578,7 +4578,7 @@
         <x:v>d279</x:v>
       </x:c>
       <x:c r="B280" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C280" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4595,7 +4595,7 @@
         <x:v>d280</x:v>
       </x:c>
       <x:c r="B281" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C281" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4610,7 +4610,7 @@
         <x:v>d281</x:v>
       </x:c>
       <x:c r="B282" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C282" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4625,7 +4625,7 @@
         <x:v>d282</x:v>
       </x:c>
       <x:c r="B283" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C283" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4640,7 +4640,7 @@
         <x:v>d283</x:v>
       </x:c>
       <x:c r="B284" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C284" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4655,7 +4655,7 @@
         <x:v>d284</x:v>
       </x:c>
       <x:c r="B285" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C285" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4672,7 +4672,7 @@
         <x:v>d285</x:v>
       </x:c>
       <x:c r="B286" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C286" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4687,7 +4687,7 @@
         <x:v>d286</x:v>
       </x:c>
       <x:c r="B287" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C287" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4702,7 +4702,7 @@
         <x:v>d287</x:v>
       </x:c>
       <x:c r="B288" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C288" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4717,7 +4717,7 @@
         <x:v>d288</x:v>
       </x:c>
       <x:c r="B289" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C289" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4732,7 +4732,7 @@
         <x:v>d289</x:v>
       </x:c>
       <x:c r="B290" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C290" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -4747,7 +4747,7 @@
         <x:v>d290</x:v>
       </x:c>
       <x:c r="B291" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C291" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4762,7 +4762,7 @@
         <x:v>d291</x:v>
       </x:c>
       <x:c r="B292" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C292" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4777,7 +4777,7 @@
         <x:v>d292</x:v>
       </x:c>
       <x:c r="B293" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C293" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4792,7 +4792,7 @@
         <x:v>d293</x:v>
       </x:c>
       <x:c r="B294" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C294" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4807,7 +4807,7 @@
         <x:v>d294</x:v>
       </x:c>
       <x:c r="B295" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C295" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4822,7 +4822,7 @@
         <x:v>d295</x:v>
       </x:c>
       <x:c r="B296" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C296" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4837,7 +4837,7 @@
         <x:v>d296</x:v>
       </x:c>
       <x:c r="B297" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C297" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4852,7 +4852,7 @@
         <x:v>d297</x:v>
       </x:c>
       <x:c r="B298" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C298" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4867,7 +4867,7 @@
         <x:v>d298</x:v>
       </x:c>
       <x:c r="B299" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C299" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4882,7 +4882,7 @@
         <x:v>d299</x:v>
       </x:c>
       <x:c r="B300" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C300" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4897,7 +4897,7 @@
         <x:v>d300</x:v>
       </x:c>
       <x:c r="B301" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C301" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4912,7 +4912,7 @@
         <x:v>d301</x:v>
       </x:c>
       <x:c r="B302" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C302" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4927,7 +4927,7 @@
         <x:v>d302</x:v>
       </x:c>
       <x:c r="B303" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C303" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4942,7 +4942,7 @@
         <x:v>d303</x:v>
       </x:c>
       <x:c r="B304" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C304" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4957,7 +4957,7 @@
         <x:v>d304</x:v>
       </x:c>
       <x:c r="B305" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C305" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4972,7 +4972,7 @@
         <x:v>d305</x:v>
       </x:c>
       <x:c r="B306" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C306" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -4987,7 +4987,7 @@
         <x:v>d306</x:v>
       </x:c>
       <x:c r="B307" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C307" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5002,7 +5002,7 @@
         <x:v>d307</x:v>
       </x:c>
       <x:c r="B308" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C308" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5017,7 +5017,7 @@
         <x:v>d308</x:v>
       </x:c>
       <x:c r="B309" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C309" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5027,12 +5027,12 @@
       </x:c>
       <x:c r="E309" s="5" t="str"/>
     </x:row>
-    <x:row r="310" ht="51" customHeight="1">
+    <x:row r="310" ht="61.5" customHeight="1">
       <x:c r="A310" s="6" t="str">
         <x:v>d309</x:v>
       </x:c>
       <x:c r="B310" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C310" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5042,12 +5042,12 @@
       </x:c>
       <x:c r="E310" s="5" t="str"/>
     </x:row>
-    <x:row r="311" ht="51" customHeight="1">
+    <x:row r="311" ht="61.5" customHeight="1">
       <x:c r="A311" s="6" t="str">
         <x:v>d310</x:v>
       </x:c>
       <x:c r="B311" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C311" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5062,7 +5062,7 @@
         <x:v>d311</x:v>
       </x:c>
       <x:c r="B312" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C312" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5072,12 +5072,12 @@
       </x:c>
       <x:c r="E312" s="5" t="str"/>
     </x:row>
-    <x:row r="313" ht="51" customHeight="1">
+    <x:row r="313" ht="61.5" customHeight="1">
       <x:c r="A313" s="6" t="str">
         <x:v>d312</x:v>
       </x:c>
       <x:c r="B313" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C313" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5092,7 +5092,7 @@
         <x:v>d313</x:v>
       </x:c>
       <x:c r="B314" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C314" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5109,7 +5109,7 @@
         <x:v>d314</x:v>
       </x:c>
       <x:c r="B315" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C315" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5126,7 +5126,7 @@
         <x:v>d315</x:v>
       </x:c>
       <x:c r="B316" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C316" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5143,7 +5143,7 @@
         <x:v>d316</x:v>
       </x:c>
       <x:c r="B317" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C317" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5159,7 +5159,7 @@
         <x:v>d317</x:v>
       </x:c>
       <x:c r="B318" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C318" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5175,7 +5175,7 @@
         <x:v>d318</x:v>
       </x:c>
       <x:c r="B319" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C319" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5185,12 +5185,12 @@
       </x:c>
       <x:c r="E319" s="5" t="str"/>
     </x:row>
-    <x:row r="320" ht="51" customHeight="1">
+    <x:row r="320" ht="61.5" customHeight="1">
       <x:c r="A320" s="6" t="str">
         <x:v>d319</x:v>
       </x:c>
       <x:c r="B320" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C320" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5200,12 +5200,12 @@
       </x:c>
       <x:c r="E320" s="5" t="str"/>
     </x:row>
-    <x:row r="321" ht="51" customHeight="1">
+    <x:row r="321" ht="61.5" customHeight="1">
       <x:c r="A321" s="6" t="str">
         <x:v>d320</x:v>
       </x:c>
       <x:c r="B321" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C321" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5215,12 +5215,12 @@
       </x:c>
       <x:c r="E321" s="5" t="str"/>
     </x:row>
-    <x:row r="322" ht="51" customHeight="1">
+    <x:row r="322" ht="61.5" customHeight="1">
       <x:c r="A322" s="6" t="str">
         <x:v>d321</x:v>
       </x:c>
       <x:c r="B322" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C322" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5236,7 +5236,7 @@
         <x:v>d322</x:v>
       </x:c>
       <x:c r="B323" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C323" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5257,7 +5257,7 @@
         <x:v>d323</x:v>
       </x:c>
       <x:c r="B324" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C324" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5267,12 +5267,12 @@
       </x:c>
       <x:c r="E324" s="5" t="str"/>
     </x:row>
-    <x:row r="325" ht="51" customHeight="1">
+    <x:row r="325" ht="61.5" customHeight="1">
       <x:c r="A325" s="6" t="str">
         <x:v>d324</x:v>
       </x:c>
       <x:c r="B325" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C325" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5287,7 +5287,7 @@
         <x:v>d325</x:v>
       </x:c>
       <x:c r="B326" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C326" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5302,7 +5302,7 @@
         <x:v>d326</x:v>
       </x:c>
       <x:c r="B327" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C327" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5317,7 +5317,7 @@
         <x:v>d327</x:v>
       </x:c>
       <x:c r="B328" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C328" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5332,7 +5332,7 @@
         <x:v>d328</x:v>
       </x:c>
       <x:c r="B329" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C329" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5342,12 +5342,12 @@
       </x:c>
       <x:c r="E329" s="5" t="str"/>
     </x:row>
-    <x:row r="330" ht="51" customHeight="1">
+    <x:row r="330" ht="61.5" customHeight="1">
       <x:c r="A330" s="6" t="str">
         <x:v>d329</x:v>
       </x:c>
       <x:c r="B330" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C330" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5362,7 +5362,7 @@
         <x:v>d330</x:v>
       </x:c>
       <x:c r="B331" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C331" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5377,7 +5377,7 @@
         <x:v>d331</x:v>
       </x:c>
       <x:c r="B332" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C332" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5392,7 +5392,7 @@
         <x:v>d332</x:v>
       </x:c>
       <x:c r="B333" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C333" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5409,7 +5409,7 @@
         <x:v>d333</x:v>
       </x:c>
       <x:c r="B334" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C334" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5425,7 +5425,7 @@
         <x:v>d334</x:v>
       </x:c>
       <x:c r="B335" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C335" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5440,7 +5440,7 @@
         <x:v>d335</x:v>
       </x:c>
       <x:c r="B336" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C336" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5455,7 +5455,7 @@
         <x:v>d336</x:v>
       </x:c>
       <x:c r="B337" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C337" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5470,7 +5470,7 @@
         <x:v>d337</x:v>
       </x:c>
       <x:c r="B338" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C338" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5485,7 +5485,7 @@
         <x:v>d338</x:v>
       </x:c>
       <x:c r="B339" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C339" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5500,7 +5500,7 @@
         <x:v>d339</x:v>
       </x:c>
       <x:c r="B340" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C340" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5515,7 +5515,7 @@
         <x:v>d340</x:v>
       </x:c>
       <x:c r="B341" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C341" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5525,12 +5525,12 @@
       </x:c>
       <x:c r="E341" s="5" t="str"/>
     </x:row>
-    <x:row r="342" ht="51" customHeight="1">
+    <x:row r="342" ht="61.5" customHeight="1">
       <x:c r="A342" s="6" t="str">
         <x:v>d341</x:v>
       </x:c>
       <x:c r="B342" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C342" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5541,12 +5541,12 @@
       </x:c>
       <x:c r="E342" s="5" t="str"/>
     </x:row>
-    <x:row r="343" ht="51" customHeight="1">
+    <x:row r="343" ht="61.5" customHeight="1">
       <x:c r="A343" s="6" t="str">
         <x:v>d342</x:v>
       </x:c>
       <x:c r="B343" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C343" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5561,7 +5561,7 @@
         <x:v>d343</x:v>
       </x:c>
       <x:c r="B344" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C344" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5576,7 +5576,7 @@
         <x:v>d344</x:v>
       </x:c>
       <x:c r="B345" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C345" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5591,7 +5591,7 @@
         <x:v>d345</x:v>
       </x:c>
       <x:c r="B346" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C346" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5606,7 +5606,7 @@
         <x:v>d346</x:v>
       </x:c>
       <x:c r="B347" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C347" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5621,7 +5621,7 @@
         <x:v>d347</x:v>
       </x:c>
       <x:c r="B348" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C348" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5650,7 +5650,7 @@
         <x:v>d348</x:v>
       </x:c>
       <x:c r="B349" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C349" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5665,7 +5665,7 @@
         <x:v>d349</x:v>
       </x:c>
       <x:c r="B350" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C350" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5680,7 +5680,7 @@
         <x:v>d350</x:v>
       </x:c>
       <x:c r="B351" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C351" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5695,7 +5695,7 @@
         <x:v>d351</x:v>
       </x:c>
       <x:c r="B352" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C352" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5710,7 +5710,7 @@
         <x:v>d352</x:v>
       </x:c>
       <x:c r="B353" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C353" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5722,12 +5722,12 @@
       </x:c>
       <x:c r="E353" s="5" t="str"/>
     </x:row>
-    <x:row r="354" ht="51" customHeight="1">
+    <x:row r="354" ht="61.5" customHeight="1">
       <x:c r="A354" s="6" t="str">
         <x:v>d353</x:v>
       </x:c>
       <x:c r="B354" s="5" t="str">
-        <x:v>Systematically generated variation; Earlier test; author not recorded</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C354" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5742,7 +5742,7 @@
         <x:v>d354</x:v>
       </x:c>
       <x:c r="B355" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C355" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5757,7 +5757,7 @@
         <x:v>d355</x:v>
       </x:c>
       <x:c r="B356" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C356" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5772,7 +5772,7 @@
         <x:v>d356</x:v>
       </x:c>
       <x:c r="B357" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C357" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5788,7 +5788,7 @@
         <x:v>d357</x:v>
       </x:c>
       <x:c r="B358" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C358" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5800,12 +5800,12 @@
       </x:c>
       <x:c r="E358" s="5" t="str"/>
     </x:row>
-    <x:row r="359" ht="51" customHeight="1">
+    <x:row r="359" ht="61.5" customHeight="1">
       <x:c r="A359" s="6" t="str">
         <x:v>d358</x:v>
       </x:c>
       <x:c r="B359" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C359" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5820,7 +5820,7 @@
         <x:v>d359</x:v>
       </x:c>
       <x:c r="B360" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C360" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5835,7 +5835,7 @@
         <x:v>d360</x:v>
       </x:c>
       <x:c r="B361" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C361" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5850,7 +5850,7 @@
         <x:v>d361</x:v>
       </x:c>
       <x:c r="B362" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C362" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5866,7 +5866,7 @@
         <x:v>d362</x:v>
       </x:c>
       <x:c r="B363" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C363" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5878,12 +5878,12 @@
       </x:c>
       <x:c r="E363" s="5" t="str"/>
     </x:row>
-    <x:row r="364" ht="51" customHeight="1">
+    <x:row r="364" ht="61.5" customHeight="1">
       <x:c r="A364" s="6" t="str">
         <x:v>d363</x:v>
       </x:c>
       <x:c r="B364" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C364" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5898,7 +5898,7 @@
         <x:v>d364</x:v>
       </x:c>
       <x:c r="B365" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C365" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5913,7 +5913,7 @@
         <x:v>d365</x:v>
       </x:c>
       <x:c r="B366" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C366" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5930,7 +5930,7 @@
         <x:v>d366</x:v>
       </x:c>
       <x:c r="B367" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C367" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5945,7 +5945,7 @@
         <x:v>d367</x:v>
       </x:c>
       <x:c r="B368" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C368" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -5960,7 +5960,7 @@
         <x:v>d368</x:v>
       </x:c>
       <x:c r="B369" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C369" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5975,7 +5975,7 @@
         <x:v>d369</x:v>
       </x:c>
       <x:c r="B370" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C370" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -5990,7 +5990,7 @@
         <x:v>d370</x:v>
       </x:c>
       <x:c r="B371" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C371" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6005,7 +6005,7 @@
         <x:v>d371</x:v>
       </x:c>
       <x:c r="B372" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C372" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6021,7 +6021,7 @@
         <x:v>d372</x:v>
       </x:c>
       <x:c r="B373" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C373" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6031,12 +6031,12 @@
       </x:c>
       <x:c r="E373" s="5" t="str"/>
     </x:row>
-    <x:row r="374" ht="51" customHeight="1">
+    <x:row r="374" ht="61.5" customHeight="1">
       <x:c r="A374" s="6" t="str">
         <x:v>d373</x:v>
       </x:c>
       <x:c r="B374" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C374" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6051,7 +6051,7 @@
         <x:v>d374</x:v>
       </x:c>
       <x:c r="B375" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C375" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6072,7 +6072,7 @@
         <x:v>d375</x:v>
       </x:c>
       <x:c r="B376" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C376" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6087,7 +6087,7 @@
         <x:v>d376</x:v>
       </x:c>
       <x:c r="B377" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C377" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6102,7 +6102,7 @@
         <x:v>d377</x:v>
       </x:c>
       <x:c r="B378" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C378" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6112,12 +6112,12 @@
       </x:c>
       <x:c r="E378" s="5" t="str"/>
     </x:row>
-    <x:row r="379" ht="57.75" customHeight="1">
+    <x:row r="379" ht="61.5" customHeight="1">
       <x:c r="A379" s="6" t="str">
         <x:v>d378</x:v>
       </x:c>
       <x:c r="B379" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C379" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6132,7 +6132,7 @@
         <x:v>d379</x:v>
       </x:c>
       <x:c r="B380" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C380" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6147,7 +6147,7 @@
         <x:v>d380</x:v>
       </x:c>
       <x:c r="B381" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C381" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6164,7 +6164,7 @@
         <x:v>d381</x:v>
       </x:c>
       <x:c r="B382" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C382" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6179,7 +6179,7 @@
         <x:v>d382</x:v>
       </x:c>
       <x:c r="B383" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C383" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6194,7 +6194,7 @@
         <x:v>d383</x:v>
       </x:c>
       <x:c r="B384" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C384" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6223,7 +6223,7 @@
         <x:v>d384</x:v>
       </x:c>
       <x:c r="B385" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C385" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6238,7 +6238,7 @@
         <x:v>d385</x:v>
       </x:c>
       <x:c r="B386" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C386" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6253,7 +6253,7 @@
         <x:v>d386</x:v>
       </x:c>
       <x:c r="B387" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C387" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6269,7 +6269,7 @@
         <x:v>d387</x:v>
       </x:c>
       <x:c r="B388" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C388" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6284,7 +6284,7 @@
         <x:v>d388</x:v>
       </x:c>
       <x:c r="B389" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C389" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6299,7 +6299,7 @@
         <x:v>d389</x:v>
       </x:c>
       <x:c r="B390" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C390" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6314,7 +6314,7 @@
         <x:v>d390</x:v>
       </x:c>
       <x:c r="B391" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C391" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6329,7 +6329,7 @@
         <x:v>d391</x:v>
       </x:c>
       <x:c r="B392" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C392" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6344,7 +6344,7 @@
         <x:v>d392</x:v>
       </x:c>
       <x:c r="B393" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C393" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>d393</x:v>
       </x:c>
       <x:c r="B394" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C394" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6376,7 +6376,7 @@
         <x:v>d394</x:v>
       </x:c>
       <x:c r="B395" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C395" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6391,7 +6391,7 @@
         <x:v>d395</x:v>
       </x:c>
       <x:c r="B396" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C396" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6406,7 +6406,7 @@
         <x:v>d396</x:v>
       </x:c>
       <x:c r="B397" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C397" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6422,7 +6422,7 @@
         <x:v>d397</x:v>
       </x:c>
       <x:c r="B398" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C398" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6439,7 +6439,7 @@
         <x:v>d398</x:v>
       </x:c>
       <x:c r="B399" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C399" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6455,12 +6455,12 @@
       </x:c>
       <x:c r="E399" s="5" t="str"/>
     </x:row>
-    <x:row r="400" ht="51" customHeight="1">
+    <x:row r="400" ht="61.5" customHeight="1">
       <x:c r="A400" s="6" t="str">
         <x:v>d399</x:v>
       </x:c>
       <x:c r="B400" s="5" t="str">
-        <x:v>Earlier test; author not recorded; Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C400" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6475,7 +6475,7 @@
         <x:v>d400</x:v>
       </x:c>
       <x:c r="B401" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C401" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6490,7 +6490,7 @@
         <x:v>d401</x:v>
       </x:c>
       <x:c r="B402" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C402" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6505,7 +6505,7 @@
         <x:v>d402</x:v>
       </x:c>
       <x:c r="B403" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C403" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6515,12 +6515,12 @@
       </x:c>
       <x:c r="E403" s="5" t="str"/>
     </x:row>
-    <x:row r="404" ht="51" customHeight="1">
+    <x:row r="404" ht="61.5" customHeight="1">
       <x:c r="A404" s="6" t="str">
         <x:v>d403</x:v>
       </x:c>
       <x:c r="B404" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C404" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6535,7 +6535,7 @@
         <x:v>d404</x:v>
       </x:c>
       <x:c r="B405" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C405" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6550,7 +6550,7 @@
         <x:v>d405</x:v>
       </x:c>
       <x:c r="B406" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C406" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6565,7 +6565,7 @@
         <x:v>d406</x:v>
       </x:c>
       <x:c r="B407" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C407" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6580,7 +6580,7 @@
         <x:v>d407</x:v>
       </x:c>
       <x:c r="B408" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C408" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6595,7 +6595,7 @@
         <x:v>d408</x:v>
       </x:c>
       <x:c r="B409" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C409" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6610,7 +6610,7 @@
         <x:v>d409</x:v>
       </x:c>
       <x:c r="B410" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C410" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6625,7 +6625,7 @@
         <x:v>d410</x:v>
       </x:c>
       <x:c r="B411" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C411" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6640,7 +6640,7 @@
         <x:v>d411</x:v>
       </x:c>
       <x:c r="B412" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C412" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6656,7 +6656,7 @@
         <x:v>d412</x:v>
       </x:c>
       <x:c r="B413" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C413" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6666,12 +6666,12 @@
       </x:c>
       <x:c r="E413" s="5" t="str"/>
     </x:row>
-    <x:row r="414" ht="51" customHeight="1">
+    <x:row r="414" ht="61.5" customHeight="1">
       <x:c r="A414" s="6" t="str">
         <x:v>d413</x:v>
       </x:c>
       <x:c r="B414" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C414" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6686,7 +6686,7 @@
         <x:v>d414</x:v>
       </x:c>
       <x:c r="B415" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C415" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6701,7 +6701,7 @@
         <x:v>d415</x:v>
       </x:c>
       <x:c r="B416" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C416" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6716,7 +6716,7 @@
         <x:v>d416</x:v>
       </x:c>
       <x:c r="B417" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C417" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6732,7 +6732,7 @@
         <x:v>d417</x:v>
       </x:c>
       <x:c r="B418" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C418" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6747,7 +6747,7 @@
         <x:v>d418</x:v>
       </x:c>
       <x:c r="B419" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C419" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6776,7 +6776,7 @@
         <x:v>d419</x:v>
       </x:c>
       <x:c r="B420" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C420" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6791,7 +6791,7 @@
         <x:v>d420</x:v>
       </x:c>
       <x:c r="B421" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C421" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6806,7 +6806,7 @@
         <x:v>d421</x:v>
       </x:c>
       <x:c r="B422" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C422" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6821,7 +6821,7 @@
         <x:v>d422</x:v>
       </x:c>
       <x:c r="B423" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C423" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6831,12 +6831,12 @@
       </x:c>
       <x:c r="E423" s="5" t="str"/>
     </x:row>
-    <x:row r="424" ht="57.75" customHeight="1">
+    <x:row r="424" ht="61.5" customHeight="1">
       <x:c r="A424" s="6" t="str">
         <x:v>d423</x:v>
       </x:c>
       <x:c r="B424" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C424" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6848,12 +6848,12 @@
       </x:c>
       <x:c r="E424" s="5" t="str"/>
     </x:row>
-    <x:row r="425" ht="51" customHeight="1">
+    <x:row r="425" ht="61.5" customHeight="1">
       <x:c r="A425" s="6" t="str">
         <x:v>d424</x:v>
       </x:c>
       <x:c r="B425" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C425" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6868,7 +6868,7 @@
         <x:v>d425</x:v>
       </x:c>
       <x:c r="B426" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C426" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6883,7 +6883,7 @@
         <x:v>d426</x:v>
       </x:c>
       <x:c r="B427" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C427" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6898,7 +6898,7 @@
         <x:v>d427</x:v>
       </x:c>
       <x:c r="B428" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C428" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6913,7 +6913,7 @@
         <x:v>d428</x:v>
       </x:c>
       <x:c r="B429" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C429" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6928,7 +6928,7 @@
         <x:v>d429</x:v>
       </x:c>
       <x:c r="B430" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C430" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6943,7 +6943,7 @@
         <x:v>d430</x:v>
       </x:c>
       <x:c r="B431" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C431" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6958,7 +6958,7 @@
         <x:v>d431</x:v>
       </x:c>
       <x:c r="B432" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C432" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -6973,7 +6973,7 @@
         <x:v>d432</x:v>
       </x:c>
       <x:c r="B433" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C433" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -6984,12 +6984,12 @@
       </x:c>
       <x:c r="E433" s="5" t="str"/>
     </x:row>
-    <x:row r="434" ht="51" customHeight="1">
+    <x:row r="434" ht="61.5" customHeight="1">
       <x:c r="A434" s="6" t="str">
         <x:v>d433</x:v>
       </x:c>
       <x:c r="B434" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C434" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7004,7 +7004,7 @@
         <x:v>d434</x:v>
       </x:c>
       <x:c r="B435" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C435" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7019,7 +7019,7 @@
         <x:v>d435</x:v>
       </x:c>
       <x:c r="B436" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C436" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7034,7 +7034,7 @@
         <x:v>d436</x:v>
       </x:c>
       <x:c r="B437" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C437" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7049,7 +7049,7 @@
         <x:v>d437</x:v>
       </x:c>
       <x:c r="B438" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C438" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7064,7 +7064,7 @@
         <x:v>d438</x:v>
       </x:c>
       <x:c r="B439" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C439" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7079,7 +7079,7 @@
         <x:v>d439</x:v>
       </x:c>
       <x:c r="B440" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C440" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7094,7 +7094,7 @@
         <x:v>d440</x:v>
       </x:c>
       <x:c r="B441" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C441" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7109,7 +7109,7 @@
         <x:v>d441</x:v>
       </x:c>
       <x:c r="B442" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C442" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7124,7 +7124,7 @@
         <x:v>d442</x:v>
       </x:c>
       <x:c r="B443" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C443" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7139,7 +7139,7 @@
         <x:v>d443</x:v>
       </x:c>
       <x:c r="B444" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C444" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7154,7 +7154,7 @@
         <x:v>d444</x:v>
       </x:c>
       <x:c r="B445" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C445" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7169,7 +7169,7 @@
         <x:v>d445</x:v>
       </x:c>
       <x:c r="B446" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C446" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7184,7 +7184,7 @@
         <x:v>d446</x:v>
       </x:c>
       <x:c r="B447" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C447" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7199,7 +7199,7 @@
         <x:v>d447</x:v>
       </x:c>
       <x:c r="B448" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C448" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7209,12 +7209,12 @@
       </x:c>
       <x:c r="E448" s="5" t="str"/>
     </x:row>
-    <x:row r="449" ht="51" customHeight="1">
+    <x:row r="449" ht="61.5" customHeight="1">
       <x:c r="A449" s="6" t="str">
         <x:v>d448</x:v>
       </x:c>
       <x:c r="B449" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C449" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7230,7 +7230,7 @@
         <x:v>d449</x:v>
       </x:c>
       <x:c r="B450" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C450" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7245,7 +7245,7 @@
         <x:v>d450</x:v>
       </x:c>
       <x:c r="B451" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C451" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7260,7 +7260,7 @@
         <x:v>d451</x:v>
       </x:c>
       <x:c r="B452" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C452" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7275,7 +7275,7 @@
         <x:v>d452</x:v>
       </x:c>
       <x:c r="B453" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C453" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7290,7 +7290,7 @@
         <x:v>d453</x:v>
       </x:c>
       <x:c r="B454" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C454" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7319,7 +7319,7 @@
         <x:v>d454</x:v>
       </x:c>
       <x:c r="B455" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C455" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7334,7 +7334,7 @@
         <x:v>d455</x:v>
       </x:c>
       <x:c r="B456" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C456" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7349,7 +7349,7 @@
         <x:v>d456</x:v>
       </x:c>
       <x:c r="B457" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C457" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7364,7 +7364,7 @@
         <x:v>d457</x:v>
       </x:c>
       <x:c r="B458" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C458" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7376,12 +7376,12 @@
       </x:c>
       <x:c r="E458" s="5" t="str"/>
     </x:row>
-    <x:row r="459" ht="51" customHeight="1">
+    <x:row r="459" ht="61.5" customHeight="1">
       <x:c r="A459" s="6" t="str">
         <x:v>d458</x:v>
       </x:c>
       <x:c r="B459" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C459" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7396,7 +7396,7 @@
         <x:v>d459</x:v>
       </x:c>
       <x:c r="B460" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C460" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7411,7 +7411,7 @@
         <x:v>d460</x:v>
       </x:c>
       <x:c r="B461" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C461" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7426,7 +7426,7 @@
         <x:v>d461</x:v>
       </x:c>
       <x:c r="B462" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C462" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7441,7 +7441,7 @@
         <x:v>d462</x:v>
       </x:c>
       <x:c r="B463" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C463" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7451,12 +7451,12 @@
       </x:c>
       <x:c r="E463" s="5" t="str"/>
     </x:row>
-    <x:row r="464" ht="57.75" customHeight="1">
+    <x:row r="464" ht="61.5" customHeight="1">
       <x:c r="A464" s="6" t="str">
         <x:v>d463</x:v>
       </x:c>
       <x:c r="B464" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C464" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7471,7 +7471,7 @@
         <x:v>d464</x:v>
       </x:c>
       <x:c r="B465" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C465" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7486,7 +7486,7 @@
         <x:v>d465</x:v>
       </x:c>
       <x:c r="B466" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C466" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7501,7 +7501,7 @@
         <x:v>d466</x:v>
       </x:c>
       <x:c r="B467" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C467" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7516,7 +7516,7 @@
         <x:v>d467</x:v>
       </x:c>
       <x:c r="B468" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C468" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7526,12 +7526,12 @@
       </x:c>
       <x:c r="E468" s="5" t="str"/>
     </x:row>
-    <x:row r="469" ht="51" customHeight="1">
+    <x:row r="469" ht="61.5" customHeight="1">
       <x:c r="A469" s="6" t="str">
         <x:v>d468</x:v>
       </x:c>
       <x:c r="B469" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C469" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7546,7 +7546,7 @@
         <x:v>d469</x:v>
       </x:c>
       <x:c r="B470" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C470" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7561,7 +7561,7 @@
         <x:v>d470</x:v>
       </x:c>
       <x:c r="B471" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C471" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7576,7 +7576,7 @@
         <x:v>d471</x:v>
       </x:c>
       <x:c r="B472" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C472" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7592,7 +7592,7 @@
         <x:v>d472</x:v>
       </x:c>
       <x:c r="B473" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C473" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7602,12 +7602,12 @@
       </x:c>
       <x:c r="E473" s="5" t="str"/>
     </x:row>
-    <x:row r="474" ht="51" customHeight="1">
+    <x:row r="474" ht="61.5" customHeight="1">
       <x:c r="A474" s="6" t="str">
         <x:v>d473</x:v>
       </x:c>
       <x:c r="B474" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C474" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7622,7 +7622,7 @@
         <x:v>d474</x:v>
       </x:c>
       <x:c r="B475" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C475" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7637,7 +7637,7 @@
         <x:v>d475</x:v>
       </x:c>
       <x:c r="B476" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C476" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7652,7 +7652,7 @@
         <x:v>d476</x:v>
       </x:c>
       <x:c r="B477" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C477" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7667,7 +7667,7 @@
         <x:v>d477</x:v>
       </x:c>
       <x:c r="B478" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C478" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7682,7 +7682,7 @@
         <x:v>d478</x:v>
       </x:c>
       <x:c r="B479" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C479" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7711,7 +7711,7 @@
         <x:v>d479</x:v>
       </x:c>
       <x:c r="B480" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C480" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7726,7 +7726,7 @@
         <x:v>d480</x:v>
       </x:c>
       <x:c r="B481" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C481" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7741,7 +7741,7 @@
         <x:v>d481</x:v>
       </x:c>
       <x:c r="B482" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C482" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7756,7 +7756,7 @@
         <x:v>d482</x:v>
       </x:c>
       <x:c r="B483" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C483" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7766,12 +7766,12 @@
       </x:c>
       <x:c r="E483" s="5" t="str"/>
     </x:row>
-    <x:row r="484" ht="51" customHeight="1">
+    <x:row r="484" ht="61.5" customHeight="1">
       <x:c r="A484" s="6" t="str">
         <x:v>d483</x:v>
       </x:c>
       <x:c r="B484" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C484" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7781,12 +7781,12 @@
       </x:c>
       <x:c r="E484" s="5" t="str"/>
     </x:row>
-    <x:row r="485" ht="57.75" customHeight="1">
+    <x:row r="485" ht="61.5" customHeight="1">
       <x:c r="A485" s="6" t="str">
         <x:v>d484</x:v>
       </x:c>
       <x:c r="B485" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C485" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7803,7 +7803,7 @@
         <x:v>d485</x:v>
       </x:c>
       <x:c r="B486" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C486" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7818,7 +7818,7 @@
         <x:v>d486</x:v>
       </x:c>
       <x:c r="B487" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C487" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7833,7 +7833,7 @@
         <x:v>d487</x:v>
       </x:c>
       <x:c r="B488" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C488" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7843,12 +7843,12 @@
       </x:c>
       <x:c r="E488" s="5" t="str"/>
     </x:row>
-    <x:row r="489" ht="57.75" customHeight="1">
+    <x:row r="489" ht="61.5" customHeight="1">
       <x:c r="A489" s="6" t="str">
         <x:v>d488</x:v>
       </x:c>
       <x:c r="B489" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C489" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7865,7 +7865,7 @@
         <x:v>d489</x:v>
       </x:c>
       <x:c r="B490" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C490" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7880,7 +7880,7 @@
         <x:v>d490</x:v>
       </x:c>
       <x:c r="B491" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C491" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7895,7 +7895,7 @@
         <x:v>d491</x:v>
       </x:c>
       <x:c r="B492" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C492" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7910,7 +7910,7 @@
         <x:v>d492</x:v>
       </x:c>
       <x:c r="B493" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C493" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7920,12 +7920,12 @@
       </x:c>
       <x:c r="E493" s="5" t="str"/>
     </x:row>
-    <x:row r="494" ht="51" customHeight="1">
+    <x:row r="494" ht="61.5" customHeight="1">
       <x:c r="A494" s="6" t="str">
         <x:v>d493</x:v>
       </x:c>
       <x:c r="B494" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C494" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7940,7 +7940,7 @@
         <x:v>d494</x:v>
       </x:c>
       <x:c r="B495" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C495" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7955,7 +7955,7 @@
         <x:v>d495</x:v>
       </x:c>
       <x:c r="B496" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C496" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7970,7 +7970,7 @@
         <x:v>d496</x:v>
       </x:c>
       <x:c r="B497" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C497" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -7985,7 +7985,7 @@
         <x:v>d497</x:v>
       </x:c>
       <x:c r="B498" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C498" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -7997,12 +7997,12 @@
       </x:c>
       <x:c r="E498" s="5" t="str"/>
     </x:row>
-    <x:row r="499" ht="51" customHeight="1">
+    <x:row r="499" ht="61.5" customHeight="1">
       <x:c r="A499" s="6" t="str">
         <x:v>d498</x:v>
       </x:c>
       <x:c r="B499" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C499" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8012,12 +8012,12 @@
       </x:c>
       <x:c r="E499" s="5" t="str"/>
     </x:row>
-    <x:row r="500" ht="51" customHeight="1">
+    <x:row r="500" ht="61.5" customHeight="1">
       <x:c r="A500" s="6" t="str">
         <x:v>d499</x:v>
       </x:c>
       <x:c r="B500" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C500" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8032,7 +8032,7 @@
         <x:v>d500</x:v>
       </x:c>
       <x:c r="B501" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C501" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8047,7 +8047,7 @@
         <x:v>d501</x:v>
       </x:c>
       <x:c r="B502" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C502" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8063,7 +8063,7 @@
         <x:v>d502</x:v>
       </x:c>
       <x:c r="B503" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C503" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8078,7 +8078,7 @@
         <x:v>d503</x:v>
       </x:c>
       <x:c r="B504" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C504" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8095,7 +8095,7 @@
         <x:v>d504</x:v>
       </x:c>
       <x:c r="B505" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C505" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8110,7 +8110,7 @@
         <x:v>d505</x:v>
       </x:c>
       <x:c r="B506" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C506" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8125,7 +8125,7 @@
         <x:v>d506</x:v>
       </x:c>
       <x:c r="B507" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C507" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8141,7 +8141,7 @@
         <x:v>d507</x:v>
       </x:c>
       <x:c r="B508" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C508" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8151,12 +8151,12 @@
       </x:c>
       <x:c r="E508" s="5" t="str"/>
     </x:row>
-    <x:row r="509" ht="51" customHeight="1">
+    <x:row r="509" ht="61.5" customHeight="1">
       <x:c r="A509" s="6" t="str">
         <x:v>d508</x:v>
       </x:c>
       <x:c r="B509" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C509" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8171,7 +8171,7 @@
         <x:v>d509</x:v>
       </x:c>
       <x:c r="B510" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C510" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8186,7 +8186,7 @@
         <x:v>d510</x:v>
       </x:c>
       <x:c r="B511" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C511" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8201,7 +8201,7 @@
         <x:v>d511</x:v>
       </x:c>
       <x:c r="B512" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C512" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8217,7 +8217,7 @@
         <x:v>d512</x:v>
       </x:c>
       <x:c r="B513" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C513" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8227,12 +8227,12 @@
       </x:c>
       <x:c r="E513" s="5" t="str"/>
     </x:row>
-    <x:row r="514" ht="51" customHeight="1">
+    <x:row r="514" ht="61.5" customHeight="1">
       <x:c r="A514" s="6" t="str">
         <x:v>d513</x:v>
       </x:c>
       <x:c r="B514" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C514" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8247,7 +8247,7 @@
         <x:v>d514</x:v>
       </x:c>
       <x:c r="B515" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C515" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8262,7 +8262,7 @@
         <x:v>d515</x:v>
       </x:c>
       <x:c r="B516" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C516" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8277,7 +8277,7 @@
         <x:v>d516</x:v>
       </x:c>
       <x:c r="B517" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C517" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8293,7 +8293,7 @@
         <x:v>d517</x:v>
       </x:c>
       <x:c r="B518" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C518" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8303,12 +8303,12 @@
       </x:c>
       <x:c r="E518" s="5" t="str"/>
     </x:row>
-    <x:row r="519" ht="51" customHeight="1">
+    <x:row r="519" ht="61.5" customHeight="1">
       <x:c r="A519" s="6" t="str">
         <x:v>d518</x:v>
       </x:c>
       <x:c r="B519" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C519" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8323,7 +8323,7 @@
         <x:v>d519</x:v>
       </x:c>
       <x:c r="B520" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C520" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8338,7 +8338,7 @@
         <x:v>d520</x:v>
       </x:c>
       <x:c r="B521" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C521" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8353,7 +8353,7 @@
         <x:v>d521</x:v>
       </x:c>
       <x:c r="B522" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C522" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8368,7 +8368,7 @@
         <x:v>d522</x:v>
       </x:c>
       <x:c r="B523" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C523" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8383,7 +8383,7 @@
         <x:v>d523</x:v>
       </x:c>
       <x:c r="B524" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C524" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8398,7 +8398,7 @@
         <x:v>d524</x:v>
       </x:c>
       <x:c r="B525" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C525" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8413,7 +8413,7 @@
         <x:v>d525</x:v>
       </x:c>
       <x:c r="B526" s="5" t="str">
-        <x:v>LLM-generated example; Earlier test; author not recorded</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C526" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8428,7 +8428,7 @@
         <x:v>d526</x:v>
       </x:c>
       <x:c r="B527" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C527" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8438,12 +8438,12 @@
       </x:c>
       <x:c r="E527" s="5" t="str"/>
     </x:row>
-    <x:row r="528" ht="51" customHeight="1">
+    <x:row r="528" ht="61.5" customHeight="1">
       <x:c r="A528" s="6" t="str">
         <x:v>d527</x:v>
       </x:c>
       <x:c r="B528" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C528" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8458,7 +8458,7 @@
         <x:v>d528</x:v>
       </x:c>
       <x:c r="B529" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C529" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8473,7 +8473,7 @@
         <x:v>d529</x:v>
       </x:c>
       <x:c r="B530" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C530" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8490,7 +8490,7 @@
         <x:v>d530</x:v>
       </x:c>
       <x:c r="B531" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C531" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8500,12 +8500,12 @@
       </x:c>
       <x:c r="E531" s="5" t="str"/>
     </x:row>
-    <x:row r="532" ht="51" customHeight="1">
+    <x:row r="532" ht="61.5" customHeight="1">
       <x:c r="A532" s="6" t="str">
         <x:v>d531</x:v>
       </x:c>
       <x:c r="B532" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C532" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8520,7 +8520,7 @@
         <x:v>d532</x:v>
       </x:c>
       <x:c r="B533" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C533" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8535,7 +8535,7 @@
         <x:v>d533</x:v>
       </x:c>
       <x:c r="B534" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C534" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8552,7 +8552,7 @@
         <x:v>d534</x:v>
       </x:c>
       <x:c r="B535" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C535" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8562,12 +8562,12 @@
       </x:c>
       <x:c r="E535" s="5" t="str"/>
     </x:row>
-    <x:row r="536" ht="51" customHeight="1">
+    <x:row r="536" ht="61.5" customHeight="1">
       <x:c r="A536" s="6" t="str">
         <x:v>d535</x:v>
       </x:c>
       <x:c r="B536" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C536" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8582,7 +8582,7 @@
         <x:v>d536</x:v>
       </x:c>
       <x:c r="B537" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C537" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8597,7 +8597,7 @@
         <x:v>d537</x:v>
       </x:c>
       <x:c r="B538" s="5" t="str">
-        <x:v>LLM-generated example</x:v>
+        <x:v>LLM-generated offer</x:v>
       </x:c>
       <x:c r="C538" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8607,12 +8607,12 @@
       </x:c>
       <x:c r="E538" s="5" t="str"/>
     </x:row>
-    <x:row r="539" ht="51" customHeight="1">
+    <x:row r="539" ht="61.5" customHeight="1">
       <x:c r="A539" s="6" t="str">
         <x:v>d538</x:v>
       </x:c>
       <x:c r="B539" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C539" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8627,7 +8627,7 @@
         <x:v>d539</x:v>
       </x:c>
       <x:c r="B540" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C540" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8642,7 +8642,7 @@
         <x:v>d540</x:v>
       </x:c>
       <x:c r="B541" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C541" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8657,7 +8657,7 @@
         <x:v>d541</x:v>
       </x:c>
       <x:c r="B542" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C542" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8672,7 +8672,7 @@
         <x:v>d542</x:v>
       </x:c>
       <x:c r="B543" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C543" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8687,7 +8687,7 @@
         <x:v>d543</x:v>
       </x:c>
       <x:c r="B544" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C544" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8697,12 +8697,12 @@
       </x:c>
       <x:c r="E544" s="5" t="str"/>
     </x:row>
-    <x:row r="545" ht="51" customHeight="1">
+    <x:row r="545" ht="61.5" customHeight="1">
       <x:c r="A545" s="6" t="str">
         <x:v>d544</x:v>
       </x:c>
       <x:c r="B545" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C545" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8717,7 +8717,7 @@
         <x:v>d545</x:v>
       </x:c>
       <x:c r="B546" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C546" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8732,7 +8732,7 @@
         <x:v>d546</x:v>
       </x:c>
       <x:c r="B547" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C547" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8744,12 +8744,12 @@
       </x:c>
       <x:c r="E547" s="5" t="str"/>
     </x:row>
-    <x:row r="548" ht="51" customHeight="1">
+    <x:row r="548" ht="61.5" customHeight="1">
       <x:c r="A548" s="6" t="str">
         <x:v>d547</x:v>
       </x:c>
       <x:c r="B548" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C548" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8764,7 +8764,7 @@
         <x:v>d548</x:v>
       </x:c>
       <x:c r="B549" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C549" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8779,7 +8779,7 @@
         <x:v>d549</x:v>
       </x:c>
       <x:c r="B550" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C550" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8794,7 +8794,7 @@
         <x:v>d550</x:v>
       </x:c>
       <x:c r="B551" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C551" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8818,12 +8818,12 @@
       </x:c>
       <x:c r="E551" s="5" t="str"/>
     </x:row>
-    <x:row r="552" ht="51" customHeight="1">
+    <x:row r="552" ht="61.5" customHeight="1">
       <x:c r="A552" s="6" t="str">
         <x:v>d551</x:v>
       </x:c>
       <x:c r="B552" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C552" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8838,7 +8838,7 @@
         <x:v>d552</x:v>
       </x:c>
       <x:c r="B553" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C553" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8848,12 +8848,12 @@
       </x:c>
       <x:c r="E553" s="5" t="str"/>
     </x:row>
-    <x:row r="554" ht="51" customHeight="1">
+    <x:row r="554" ht="61.5" customHeight="1">
       <x:c r="A554" s="6" t="str">
         <x:v>d553</x:v>
       </x:c>
       <x:c r="B554" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C554" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8868,7 +8868,7 @@
         <x:v>d554</x:v>
       </x:c>
       <x:c r="B555" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C555" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8883,7 +8883,7 @@
         <x:v>d555</x:v>
       </x:c>
       <x:c r="B556" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C556" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8898,7 +8898,7 @@
         <x:v>d556</x:v>
       </x:c>
       <x:c r="B557" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C557" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8913,7 +8913,7 @@
         <x:v>d557</x:v>
       </x:c>
       <x:c r="B558" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C558" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8928,7 +8928,7 @@
         <x:v>d558</x:v>
       </x:c>
       <x:c r="B559" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C559" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8938,12 +8938,12 @@
       </x:c>
       <x:c r="E559" s="5" t="str"/>
     </x:row>
-    <x:row r="560" ht="57.75" customHeight="1">
+    <x:row r="560" ht="61.5" customHeight="1">
       <x:c r="A560" s="6" t="str">
         <x:v>d559</x:v>
       </x:c>
       <x:c r="B560" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C560" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8958,7 +8958,7 @@
         <x:v>d560</x:v>
       </x:c>
       <x:c r="B561" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C561" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -8973,7 +8973,7 @@
         <x:v>d561</x:v>
       </x:c>
       <x:c r="B562" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C562" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -8983,12 +8983,12 @@
       </x:c>
       <x:c r="E562" s="5" t="str"/>
     </x:row>
-    <x:row r="563" ht="51" customHeight="1">
+    <x:row r="563" ht="61.5" customHeight="1">
       <x:c r="A563" s="6" t="str">
         <x:v>d562</x:v>
       </x:c>
       <x:c r="B563" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C563" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -9003,7 +9003,7 @@
         <x:v>d563</x:v>
       </x:c>
       <x:c r="B564" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C564" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -9018,7 +9018,7 @@
         <x:v>d564</x:v>
       </x:c>
       <x:c r="B565" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C565" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -9028,12 +9028,12 @@
       </x:c>
       <x:c r="E565" s="5" t="str"/>
     </x:row>
-    <x:row r="566" ht="51" customHeight="1">
+    <x:row r="566" ht="61.5" customHeight="1">
       <x:c r="A566" s="6" t="str">
         <x:v>d565</x:v>
       </x:c>
       <x:c r="B566" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C566" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -9048,7 +9048,7 @@
         <x:v>d566</x:v>
       </x:c>
       <x:c r="B567" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C567" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -9063,7 +9063,7 @@
         <x:v>d567</x:v>
       </x:c>
       <x:c r="B568" s="5" t="str">
-        <x:v>Earlier test; author not recorded</x:v>
+        <x:v>Researcher-developed offer</x:v>
       </x:c>
       <x:c r="C568" s="5" t="str">
         <x:v>Recruiter</x:v>
@@ -9073,12 +9073,12 @@
       </x:c>
       <x:c r="E568" s="5" t="str"/>
     </x:row>
-    <x:row r="569" ht="51" customHeight="1">
+    <x:row r="569" ht="61.5" customHeight="1">
       <x:c r="A569" s="6" t="str">
         <x:v>d568</x:v>
       </x:c>
       <x:c r="B569" s="5" t="str">
-        <x:v>Systematically generated variation</x:v>
+        <x:v>Offer generated by researcher by systematically varying specific elements</x:v>
       </x:c>
       <x:c r="C569" s="5" t="str">
         <x:v>Candidate</x:v>
@@ -9091,7 +9091,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8262e36d0a574261"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07c7925f417c40c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9171,7 +9171,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8eb538904ae4e2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d142726f2c142be"/>
   </x:tableParts>
 </x:worksheet>
 </file>